--- a/Inflation.xlsx
+++ b/Inflation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marinercapital-my.sharepoint.com/personal/pgazzano_marinercapital_com/Documents/Attachments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4670" documentId="8_{5BC9BF22-D5E1-40C8-8EF5-84AC04A4E172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17B74149-C049-4506-8ACC-F39002BFDAB4}"/>
+  <xr:revisionPtr revIDLastSave="4718" documentId="8_{5BC9BF22-D5E1-40C8-8EF5-84AC04A4E172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DBB3529-CE66-4262-AA42-92A99E1AD2F5}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="1" xr2:uid="{67299944-7FF9-49B4-A72F-BD4B4EE2DA64}"/>
+    <workbookView xWindow="5070" yWindow="4095" windowWidth="28800" windowHeight="17505" activeTab="1" xr2:uid="{67299944-7FF9-49B4-A72F-BD4B4EE2DA64}"/>
   </bookViews>
   <sheets>
     <sheet name="QuantWare" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="spotDate">Sheet1!$D$11</definedName>
     <definedName name="strippingDate">Sheet1!$D$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1862,7 +1862,7 @@
     <numFmt numFmtId="170" formatCode="0.000"/>
     <numFmt numFmtId="171" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="172" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.000000_);_(* \(#,##0.000000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="173" formatCode="_(* #,##0.000000_);_(* \(#,##0.000000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -2023,7 +2023,7 @@
     <xf numFmtId="22" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2060,8 +2060,7 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="173" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2091,117 +2090,117 @@
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...3155729628</v>
+        <v>#N/A Requesting Data...4014419524</v>
         <stp/>
         <stp>BDP|16992731541288536763</stp>
         <tr r="C47" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1639696837</v>
+        <v>#N/A Requesting Data...4107491620</v>
         <stp/>
         <stp>BDP|17441981385548469415</stp>
         <tr r="C147" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1913221632</v>
+        <v>#N/A Requesting Data...4106600854</v>
         <stp/>
         <stp>BDP|16823300664420383917</stp>
         <tr r="AF15" s="1"/>
         <tr r="C85" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1954532055</v>
+        <v>#N/A Requesting Data...4049402893</v>
         <stp/>
         <stp>BDP|16104534607308324160</stp>
         <tr r="C94" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1482027718</v>
+        <v>#N/A Requesting Data...3874094250</v>
         <stp/>
         <stp>BDP|14000381530049220788</stp>
         <tr r="I25" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3691723697</v>
+        <v>#N/A Requesting Data...4088880544</v>
         <stp/>
         <stp>BDP|13618062996597023700</stp>
         <tr r="C133" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1304036496</v>
+        <v>#N/A Requesting Data...3773159105</v>
         <stp/>
         <stp>BDP|17796553259829473542</stp>
         <tr r="AF5" s="1"/>
         <tr r="C74" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3513330003</v>
+        <v>#N/A Requesting Data...3997362260</v>
         <stp/>
         <stp>BDP|11686869327268789806</stp>
         <tr r="C93" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3388671834</v>
+        <v>#N/A Requesting Data...3879526518</v>
         <stp/>
         <stp>BDP|11254996630569760992</stp>
         <tr r="C125" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2305151974</v>
+        <v>#N/A Requesting Data...3870966933</v>
         <stp/>
         <stp>BDP|13612015264399033752</stp>
         <tr r="V10" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2098765324</v>
+        <v>#N/A Requesting Data...3768459673</v>
         <stp/>
         <stp>BDP|14079966014713726781</stp>
         <tr r="C127" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2333332787</v>
+        <v>#N/A Requesting Data...3775138584</v>
         <stp/>
         <stp>BDP|11610845028872276145</stp>
         <tr r="I29" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3995530022</v>
+        <v>#N/A Requesting Data...4262051169</v>
         <stp/>
         <stp>BDP|14672533486751855074</stp>
         <tr r="C124" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1391140872</v>
+        <v>#N/A Requesting Data...4229746308</v>
         <stp/>
         <stp>BDP|17211020683026650195</stp>
         <tr r="C138" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3482081210</v>
+        <v>#N/A Requesting Data...4207223678</v>
         <stp/>
         <stp>BDP|15922667237158126089</stp>
         <tr r="C39" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2286100432</v>
+        <v>#N/A Requesting Data...3973788957</v>
         <stp/>
         <stp>BDP|16094027085626196074</stp>
         <tr r="C11" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1970540860</v>
+        <v>#N/A Requesting Data...3834133636</v>
         <stp/>
         <stp>BDP|15407879862292613179</stp>
         <tr r="C137" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1295336086</v>
+        <v>#N/A Requesting Data...4209113431</v>
         <stp/>
         <stp>BDP|15985719489993665142</stp>
         <tr r="I6" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2799692971</v>
+        <v>#N/A Requesting Data...3833622493</v>
         <stp/>
         <stp>BDP|12763602035166936982</stp>
         <tr r="C148" s="3"/>
@@ -2215,395 +2214,401 @@
         <tr r="T7" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2533731207</v>
+        <v>#N/A Requesting Data...3047925643</v>
         <stp/>
         <stp>BDP|16166135517967557952</stp>
         <tr r="C132" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4031243140</v>
+        <v>#N/A Requesting Data...3670839541</v>
         <stp/>
         <stp>BDP|17940409158619316760</stp>
         <tr r="C142" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3253477041</v>
+        <v>#N/A Requesting Data...3383964544</v>
         <stp/>
         <stp>BDP|17216665397240952135</stp>
         <tr r="I17" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3197751905</v>
+        <v>#N/A Requesting Data...3307816427</v>
         <stp/>
         <stp>BDP|18019433634783990550</stp>
         <tr r="W12" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3234414167</v>
+        <v>#N/A Requesting Data...3205456217</v>
         <stp/>
         <stp>BDP|18103056307516801704</stp>
         <tr r="I26" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1886011336</v>
+        <v>#N/A Requesting Data...3496354378</v>
         <stp/>
         <stp>BDP|10391992824295341769</stp>
         <tr r="I39" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4104215391</v>
+        <v>#N/A Requesting Data...3975060197</v>
         <stp/>
         <stp>BDP|16844649074268040624</stp>
         <tr r="AE16" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3167783338</v>
+        <v>#N/A Requesting Data...3641824060</v>
         <stp/>
         <stp>BDP|10096235586877124490</stp>
         <tr r="I13" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1849625593</v>
+        <v>#N/A Requesting Data...4112451505</v>
         <stp/>
         <stp>BDP|10266403270799696389</stp>
         <tr r="C40" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3162347837</v>
+        <v>#N/A Requesting Data...3678374485</v>
         <stp/>
         <stp>BDP|11425990669214060384</stp>
         <tr r="I47" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1662256687</v>
+        <v>#N/A Requesting Data...3938117955</v>
         <stp/>
         <stp>BDP|10949768593410598761</stp>
         <tr r="I73" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3824768085</v>
+        <v>#N/A Requesting Data...3033935024</v>
         <stp/>
         <stp>BDP|10439160437642326946</stp>
         <tr r="AF16" s="1"/>
         <tr r="C86" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3567830231</v>
+        <v>#N/A Requesting Data...3418178684</v>
         <stp/>
         <stp>BDP|16882700591339832859</stp>
         <tr r="C111" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1951955005</v>
+        <v>#N/A Requesting Data...4244639214</v>
         <stp/>
         <stp>BDP|14170015680415757018</stp>
         <tr r="AE7" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3220611498</v>
+        <v>#N/A Requesting Data...3787935173</v>
         <stp/>
         <stp>BDP|17611243686320531382</stp>
         <tr r="I59" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3891626701</v>
+        <v>#N/A Requesting Data...3184847500</v>
         <stp/>
         <stp>BDP|11918829406737250071</stp>
         <tr r="I14" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3976775457</v>
+        <v>#N/A Requesting Data...3291590101</v>
         <stp/>
         <stp>BDP|16854832033436138544</stp>
         <tr r="C155" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3517235477</v>
+        <v>#N/A Requesting Data...3366747102</v>
         <stp/>
         <stp>BDP|17277042607970816970</stp>
         <tr r="C107" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4095013943</v>
+        <v>#N/A Requesting Data...3815712752</v>
         <stp/>
         <stp>BDP|17998578082714402060</stp>
         <tr r="C6" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3871002787</v>
+        <v>#N/A Requesting Data...3462787988</v>
         <stp/>
         <stp>BDP|10193350955170613871</stp>
         <tr r="C88" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1577650544</v>
+        <v>#N/A Requesting Data...3555242654</v>
         <stp/>
         <stp>BDP|18190172375590154027</stp>
         <tr r="W9" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1725755215</v>
+        <v>#N/A Requesting Data...3019609949</v>
         <stp/>
         <stp>BDP|15409909570243670676</stp>
         <tr r="C7" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2381189204</v>
+        <v>#N/A Requesting Data...3532149590</v>
         <stp/>
         <stp>BDP|15569719439659786703</stp>
         <tr r="C31" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2119412698</v>
+        <v>#N/A Requesting Data...3304234675</v>
         <stp/>
         <stp>BDP|13008418403139983145</stp>
         <tr r="I46" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2876396833</v>
+        <v>#N/A Requesting Data...3271689006</v>
         <stp/>
         <stp>BDP|15405122576505065908</stp>
         <tr r="V5" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3765943002</v>
+        <v>#N/A Requesting Data...3501735357</v>
         <stp/>
         <stp>BDP|17170955494088651062</stp>
         <tr r="AE15" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4097337710</v>
+        <v>#N/A Requesting Data...3455401460</v>
         <stp/>
         <stp>BDP|13376976025412533562</stp>
         <tr r="V13" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2361421271</v>
+        <v>#N/A Requesting Data...3433571306</v>
         <stp/>
         <stp>BDP|10161399052818535276</stp>
         <tr r="C51" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2739273994</v>
+        <v>#N/A Requesting Data...3504263974</v>
         <stp/>
         <stp>BDP|18169528328365199626</stp>
         <tr r="W13" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3443202116</v>
+        <v>#N/A Requesting Data...3380900856</v>
         <stp/>
         <stp>BDP|10201197039248094690</stp>
         <tr r="I9" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3967208950</v>
+        <v>#N/A Requesting Data...3556078343</v>
         <stp/>
         <stp>BDP|10089418345044912817</stp>
         <tr r="C154" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3293436360</v>
+        <v>#N/A Requesting Data...3795539828</v>
         <stp/>
         <stp>BDP|14277400349200350878</stp>
         <tr r="W10" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1948705772</v>
+        <v>#N/A Requesting Data...4143113548</v>
         <stp/>
         <stp>BDP|17122786846908926017</stp>
         <tr r="V9" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1595008380</v>
+        <v>#N/A Requesting Data...3175239062</v>
         <stp/>
         <stp>BDP|16368593729568206565</stp>
         <tr r="I27" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2911108425</v>
+        <v>#N/A Requesting Data...3385540415</v>
         <stp/>
         <stp>BDP|12771767702650217891</stp>
         <tr r="C122" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3352250463</v>
+        <v>#N/A Requesting Data...3402832431</v>
         <stp/>
         <stp>BDP|15688574989692869788</stp>
         <tr r="AE4" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4235706179</v>
+        <v>#N/A Requesting Data...3395766155</v>
         <stp/>
         <stp>BDP|10069874117551329525</stp>
         <tr r="AK10" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1636200737</v>
+        <v>#N/A Requesting Data...3294547772</v>
         <stp/>
         <stp>BDP|13723237952388691137</stp>
         <tr r="I60" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1970764072</v>
+        <v>#N/A Requesting Data...3259414097</v>
         <stp/>
         <stp>BDP|15792251865835196930</stp>
         <tr r="C61" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2390515348</v>
+        <v>#N/A Requesting Data...3333124657</v>
         <stp/>
         <stp>BDP|17348010560575754900</stp>
         <tr r="AF9" s="1"/>
         <tr r="C78" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2770978510</v>
+        <v>#N/A Requesting Data...4059364067</v>
         <stp/>
         <stp>BDP|13850828028222234643</stp>
         <tr r="AK12" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1862523809</v>
+        <v>#N/A N/A</v>
+        <stp/>
+        <stp>BDH|11792853759979826874</stp>
+        <tr r="K3" s="1"/>
+      </tp>
+      <tp t="s">
+        <v>#N/A Requesting Data...3311452541</v>
         <stp/>
         <stp>BDP|11843315733840319306</stp>
         <tr r="C30" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3391688847</v>
+        <v>#N/A Requesting Data...3634916113</v>
         <stp/>
         <stp>BDP|12539778833923851723</stp>
         <tr r="I4" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1548114766</v>
+        <v>#N/A Requesting Data...3798376500</v>
         <stp/>
         <stp>BDP|15948974743108575243</stp>
         <tr r="C139" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3014976389</v>
+        <v>#N/A Requesting Data...4139349242</v>
         <stp/>
         <stp>BDP|14510679863436763091</stp>
         <tr r="C120" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2691111969</v>
+        <v>#N/A Requesting Data...3741898711</v>
         <stp/>
         <stp>BDP|15423337468220010200</stp>
         <tr r="C48" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2674547222</v>
+        <v>#N/A Requesting Data...4226160452</v>
         <stp/>
         <stp>BDP|16554250964053323391</stp>
         <tr r="C140" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3331831747</v>
+        <v>#N/A Requesting Data...4290429239</v>
         <stp/>
         <stp>BDP|16592160652608667810</stp>
         <tr r="AF8" s="1"/>
         <tr r="C77" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1983549664</v>
+        <v>#N/A Requesting Data...3205897689</v>
         <stp/>
         <stp>BDP|17581209526214633130</stp>
         <tr r="I22" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3896097499</v>
+        <v>#N/A Requesting Data...4159142663</v>
         <stp/>
         <stp>BDP|17790067849286391665</stp>
         <tr r="C153" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2916895722</v>
+        <v>#N/A Requesting Data...3092851045</v>
         <stp/>
         <stp>BDP|13848414330300524717</stp>
         <tr r="C25" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1752808058</v>
+        <v>#N/A Requesting Data...3761821609</v>
         <stp/>
         <stp>BDP|14414742449277677333</stp>
         <tr r="I48" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1916959323</v>
+        <v>#N/A Requesting Data...3356659773</v>
         <stp/>
         <stp>BDP|10431525984949135731</stp>
         <tr r="AE6" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3791658991</v>
+        <v>#N/A Requesting Data...3744863685</v>
         <stp/>
         <stp>BDP|15245373431663059562</stp>
         <tr r="C45" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4159367953</v>
+        <v>#N/A Requesting Data...3949076373</v>
         <stp/>
         <stp>BDP|16400223992249703771</stp>
         <tr r="C36" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2395861803</v>
+        <v>#N/A Requesting Data...3230205417</v>
         <stp/>
         <stp>BDP|13306033102620776023</stp>
         <tr r="I56" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2476777605</v>
+        <v>#N/A Requesting Data...4087208095</v>
         <stp/>
         <stp>BDP|14212899810107505982</stp>
         <tr r="I35" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3271826261</v>
+        <v>#N/A Requesting Data...3926441733</v>
         <stp/>
         <stp>BDP|15868782608511683085</stp>
         <tr r="I11" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3055418831</v>
+        <v>#N/A Requesting Data...3984968390</v>
         <stp/>
         <stp>BDP|17979515276474716106</stp>
         <tr r="I71" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3196040688</v>
+        <v>#N/A Requesting Data...3959880582</v>
         <stp/>
         <stp>BDP|10778957143819306480</stp>
         <tr r="C71" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2691230505</v>
+        <v>#N/A Requesting Data...3469453988</v>
         <stp/>
         <stp>BDP|12688448013157483092</stp>
         <tr r="C63" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2951881577</v>
+        <v>#N/A Requesting Data...3699221687</v>
         <stp/>
         <stp>BDP|12731169093339220353</stp>
         <tr r="AF17" s="1"/>
         <tr r="C87" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2964728000</v>
+        <v>#N/A Requesting Data...3325709898</v>
         <stp/>
         <stp>BDP|12647196816636675482</stp>
         <tr r="C13" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3498493776</v>
+        <v>#N/A Requesting Data...4100242784</v>
         <stp/>
         <stp>BDP|11165722673805264442</stp>
         <tr r="V14" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3527318251</v>
+        <v>#N/A Requesting Data...4005998743</v>
         <stp/>
         <stp>BDP|15304390986719897723</stp>
         <tr r="I76" s="3"/>
@@ -2617,25 +2622,25 @@
         <tr r="T15" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3068373711</v>
+        <v>#N/A Requesting Data...3396451216</v>
         <stp/>
         <stp>BDP|17056094946115101730</stp>
         <tr r="C50" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3038358642</v>
+        <v>#N/A Requesting Data...3452220894</v>
         <stp/>
         <stp>BDP|12482341349384741022</stp>
         <tr r="C92" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1697728374</v>
+        <v>#N/A Requesting Data...4002731228</v>
         <stp/>
         <stp>BDP|10035372776576778398</stp>
         <tr r="C151" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4024827129</v>
+        <v>#N/A Requesting Data...3331749630</v>
         <stp/>
         <stp>BDP|10572518377996429593</stp>
         <tr r="C134" s="3"/>
@@ -2649,188 +2654,188 @@
         <tr r="T8" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2564773346</v>
+        <v>#N/A Requesting Data...4213261941</v>
         <stp/>
         <stp>BDP|14164033904596541345</stp>
         <tr r="C150" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4047553863</v>
+        <v>#N/A Requesting Data...4053326486</v>
         <stp/>
         <stp>BDP|10277563748234944425</stp>
         <tr r="C70" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1774150200</v>
+        <v>#N/A Requesting Data...3743146282</v>
         <stp/>
         <stp>BDP|15558992728378959052</stp>
         <tr r="C157" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1609285708</v>
+        <v>#N/A Requesting Data...3136215487</v>
         <stp/>
         <stp>BDP|16966155604549938892</stp>
         <tr r="V15" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2124957220</v>
+        <v>#N/A Requesting Data...3792948308</v>
         <stp/>
         <stp>BDP|16630171868172310578</stp>
         <tr r="C116" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2852890850</v>
+        <v>#N/A Requesting Data...3756896790</v>
         <stp/>
         <stp>BDP|14911167774876199256</stp>
         <tr r="AE11" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2345144129</v>
+        <v>#N/A Requesting Data...3492157247</v>
         <stp/>
         <stp>BDP|18140782390732147273</stp>
         <tr r="W6" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1989350400</v>
+        <v>#N/A Requesting Data...4100572331</v>
         <stp/>
         <stp>BDP|14358713536591913732</stp>
         <tr r="C156" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3918097732</v>
+        <v>#N/A Requesting Data...4150508915</v>
         <stp/>
         <stp>BDP|16141034773411586653</stp>
         <tr r="C33" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1816539478</v>
+        <v>#N/A Requesting Data...3243083281</v>
         <stp/>
         <stp>BDP|10200710664763406425</stp>
         <tr r="AE14" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2982775689</v>
+        <v>#N/A Requesting Data...3257851166</v>
         <stp/>
         <stp>BDP|12094558219224430496</stp>
         <tr r="I49" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4136682983</v>
+        <v>#N/A Requesting Data...3196505196</v>
         <stp/>
         <stp>BDP|16156359880729322243</stp>
         <tr r="C32" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2428000674</v>
+        <v>#N/A Requesting Data...3862400645</v>
         <stp/>
         <stp>BDP|15948321080311984908</stp>
         <tr r="I5" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3996310824</v>
+        <v>#N/A Requesting Data...3564603911</v>
         <stp/>
         <stp>BDP|17218052059356947231</stp>
         <tr r="I53" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2998108425</v>
+        <v>#N/A Requesting Data...3225528102</v>
         <stp/>
         <stp>BDP|16811994797920872091</stp>
         <tr r="I30" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2419100629</v>
+        <v>#N/A Requesting Data...4143879861</v>
         <stp/>
         <stp>BDP|14453384572801610619</stp>
         <tr r="I23" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3023863129</v>
+        <v>#N/A Requesting Data...3567939655</v>
         <stp/>
         <stp>BDP|14133672355676181691</stp>
         <tr r="AF11" s="1"/>
         <tr r="C80" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3616864427</v>
+        <v>#N/A Requesting Data...3818986966</v>
         <stp/>
         <stp>BDP|14412490661036598757</stp>
         <tr r="W14" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2720094406</v>
+        <v>#N/A Requesting Data...3465568499</v>
         <stp/>
         <stp>BDP|15170971991113066182</stp>
         <tr r="C52" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2586180194</v>
+        <v>#N/A Requesting Data...4062049406</v>
         <stp/>
         <stp>BDP|13697562200646106730</stp>
         <tr r="C95" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2859135863</v>
+        <v>#N/A Requesting Data...3871173250</v>
         <stp/>
         <stp>BDP|15636417672138478943</stp>
         <tr r="C10" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2123700646</v>
+        <v>#N/A Requesting Data...3374975053</v>
         <stp/>
         <stp>BDP|16484417675794106582</stp>
         <tr r="I3" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4254173888</v>
+        <v>#N/A Requesting Data...3417545773</v>
         <stp/>
         <stp>BDP|12975895672638204195</stp>
         <tr r="C114" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2925029613</v>
+        <v>#N/A Requesting Data...3152692539</v>
         <stp/>
         <stp>BDP|11600197301772388656</stp>
         <tr r="C118" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2581434718</v>
+        <v>#N/A Requesting Data...3424633636</v>
         <stp/>
         <stp>BDP|13197414718614244628</stp>
         <tr r="I52" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3786355680</v>
+        <v>#N/A Requesting Data...3449181590</v>
         <stp/>
         <stp>BDP|16134319015750831018</stp>
         <tr r="C12" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2225596875</v>
+        <v>#N/A Requesting Data...3757317433</v>
         <stp/>
         <stp>BDP|13916844794424712219</stp>
         <tr r="I70" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2344655958</v>
+        <v>#N/A Requesting Data...4227929741</v>
         <stp/>
         <stp>BDP|13001255852371146195</stp>
         <tr r="C18" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3535902662</v>
+        <v>#N/A Requesting Data...3486214581</v>
         <stp/>
         <stp>BDP|10472707553534432264</stp>
         <tr r="C46" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3338129071</v>
+        <v>#N/A Requesting Data...3186211672</v>
         <stp/>
         <stp>BDP|13672224711066528251</stp>
         <tr r="C131" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3673268608</v>
+        <v>#N/A Requesting Data...4236519150</v>
         <stp/>
         <stp>BDP|12536746671673215567</stp>
         <tr r="AK4" s="1"/>
@@ -2844,60 +2849,62 @@
         <tr r="T10" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3975269209</v>
+        <v>#N/A Requesting Data...3976707310</v>
         <stp/>
         <stp>BDP|15629013929185250743</stp>
         <tr r="AF13" s="1"/>
         <tr r="C82" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3685061926</v>
+        <v>#N/A Requesting Data...4105708661</v>
         <stp/>
         <stp>BDP|15561826719479490000</stp>
         <tr r="I32" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3031719355</v>
+        <v>#N/A Requesting Data...3385860831</v>
         <stp/>
         <stp>BDP|11603244106841953730</stp>
         <tr r="C113" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4275407078</v>
+        <v>#N/A Requesting Data...4216948496</v>
         <stp/>
         <stp>BDP|10982893394443299785</stp>
         <tr r="W7" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1821346841</v>
+        <v>#N/A Requesting Data...4046053283</v>
         <stp/>
         <stp>BDP|16846227505238851942</stp>
         <tr r="I66" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3312192108</v>
+        <v>#N/A Requesting Data...4000865166</v>
         <stp/>
         <stp>BDP|12955848023335935850</stp>
         <tr r="V11" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1947949182</v>
+        <v>#N/A Requesting Data...4213952964</v>
         <stp/>
         <stp>BDP|15789438722520061638</stp>
         <tr r="C56" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2574227802</v>
+        <v>#N/A Requesting Data...3871316745</v>
         <stp/>
         <stp>BDP|16132012335723119300</stp>
         <tr r="I51" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3991338997</v>
+        <v>#N/A Requesting Data...4134993618</v>
         <stp/>
         <stp>BDP|13223727566213658474</stp>
         <tr r="C4" s="3"/>
       </tp>
+    </main>
+    <main first="bofaddin.rtdserver">
       <tp t="s">
         <v>3/1/2026</v>
         <stp/>
@@ -2915,859 +2922,853 @@
         <tr r="T11" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4222387547</v>
+        <v>#N/A Requesting Data...3647775575</v>
         <stp/>
         <stp>BDP|8883858632779658642</stp>
         <tr r="C35" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1998722045</v>
+        <v>#N/A Requesting Data...4199277891</v>
         <stp/>
         <stp>BDP|3086350895877252240</stp>
         <tr r="C16" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4027395473</v>
+        <v>#N/A Requesting Data...3524664389</v>
         <stp/>
         <stp>BDP|8438578538283438076</stp>
         <tr r="C141" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2827512856</v>
+        <v>#N/A Requesting Data...3386950113</v>
         <stp/>
         <stp>BDP|6588650681734761183</stp>
         <tr r="C27" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1802688589</v>
+        <v>#N/A Requesting Data...3553523792</v>
         <stp/>
         <stp>BDP|3444084880003121533</stp>
         <tr r="C60" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2077781147</v>
+        <v>#N/A Requesting Data...3250700605</v>
         <stp/>
         <stp>BDP|6909868581922049918</stp>
         <tr r="C110" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2145238789</v>
+        <v>#N/A Requesting Data...3714756591</v>
         <stp/>
         <stp>BDP|1445557879826346863</stp>
         <tr r="I40" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1799827062</v>
+        <v>#N/A Requesting Data...3891873231</v>
         <stp/>
         <stp>BDP|9950524043497247294</stp>
         <tr r="C136" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3826590396</v>
+        <v>#N/A Requesting Data...3495014803</v>
         <stp/>
         <stp>BDP|9710156432571566758</stp>
         <tr r="I37" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2909310914</v>
+        <v>#N/A Requesting Data...3518606931</v>
         <stp/>
         <stp>BDP|5663303020590277926</stp>
         <tr r="C98" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2194150963</v>
+        <v>#N/A Requesting Data...3983087632</v>
         <stp/>
         <stp>BDP|2199406980220213375</stp>
         <tr r="C5" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4061016005</v>
+        <v>#N/A Requesting Data...3794210885</v>
         <stp/>
         <stp>BDP|4217561534179612625</stp>
         <tr r="C58" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3300629138</v>
+        <v>#N/A Requesting Data...3456376019</v>
         <stp/>
         <stp>BDP|2180948075766112744</stp>
         <tr r="C130" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3093790700</v>
+        <v>#N/A Requesting Data...3403762297</v>
         <stp/>
         <stp>BDP|7901956006278721869</stp>
         <tr r="C104" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4268758088</v>
+        <v>#N/A Requesting Data...4216517916</v>
         <stp/>
         <stp>BDP|7411893423245165667</stp>
         <tr r="C2" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2718582398</v>
+        <v>#N/A Requesting Data...3746737784</v>
         <stp/>
         <stp>BDP|5391621699753663705</stp>
         <tr r="C100" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3479847780</v>
+        <v>#N/A Requesting Data...4165333707</v>
         <stp/>
         <stp>BDP|1569781952234888993</stp>
         <tr r="V8" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3718896850</v>
+        <v>#N/A Requesting Data...4218479745</v>
         <stp/>
         <stp>BDP|4672226517939820059</stp>
         <tr r="C117" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2263922935</v>
+        <v>#N/A Requesting Data...3993868111</v>
         <stp/>
         <stp>BDP|3800842490174647867</stp>
         <tr r="C109" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3058710068</v>
+        <v>#N/A Requesting Data...4223389853</v>
         <stp/>
         <stp>BDP|5709225380357404601</stp>
         <tr r="C149" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2881581373</v>
+        <v>#N/A Requesting Data...4144938921</v>
         <stp/>
         <stp>BDP|5085189328000745819</stp>
         <tr r="C112" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3038890494</v>
+        <v>#N/A Requesting Data...3696695367</v>
         <stp/>
         <stp>BDP|9382709674166745175</stp>
         <tr r="AE5" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3043669962</v>
+        <v>#N/A Requesting Data...4181540796</v>
         <stp/>
         <stp>BDP|2340626784505790767</stp>
         <tr r="I64" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3599936394</v>
+        <v>#N/A Requesting Data...3933103288</v>
         <stp/>
         <stp>BDP|8152802095095796271</stp>
         <tr r="C146" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2177832124</v>
+        <v>#N/A Requesting Data...3973468462</v>
         <stp/>
         <stp>BDP|9651250663630176343</stp>
         <tr r="W8" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4009122505</v>
+        <v>#N/A Requesting Data...3379167498</v>
         <stp/>
         <stp>BDP|5586141029318235107</stp>
         <tr r="I8" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2826817992</v>
+        <v>#N/A Requesting Data...3297644125</v>
         <stp/>
         <stp>BDP|3942884404210820458</stp>
         <tr r="I67" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2299646328</v>
+        <v>#N/A Requesting Data...3571360720</v>
         <stp/>
         <stp>BDP|3410021422558947640</stp>
         <tr r="I41" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1803241645</v>
+        <v>#N/A Requesting Data...3870858391</v>
         <stp/>
         <stp>BDP|7821635165939358110</stp>
         <tr r="AF6" s="1"/>
         <tr r="C75" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3316773881</v>
+        <v>#N/A Requesting Data...3954314880</v>
         <stp/>
         <stp>BDP|8099192118667719026</stp>
         <tr r="C42" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3899736741</v>
+        <v>#N/A Requesting Data...4200125674</v>
         <stp/>
         <stp>BDP|7564342032061205950</stp>
         <tr r="C145" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3091965159</v>
+        <v>#N/A Requesting Data...4196329852</v>
         <stp/>
         <stp>BDP|6558427909622035868</stp>
         <tr r="C15" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3445324269</v>
+        <v>#N/A Requesting Data...3369833809</v>
         <stp/>
         <stp>BDP|9888060838461771394</stp>
         <tr r="V4" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4177211298</v>
+        <v>#N/A Requesting Data...3754259908</v>
         <stp/>
         <stp>BDP|8314771832905317181</stp>
         <tr r="C128" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3169112536</v>
+        <v>#N/A Requesting Data...4179253388</v>
         <stp/>
         <stp>BDP|1996573356248002191</stp>
         <tr r="AK5" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4211469348</v>
+        <v>#N/A Requesting Data...3625149006</v>
         <stp/>
         <stp>BDP|4081049616208229565</stp>
         <tr r="C20" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2971837175</v>
+        <v>#N/A Requesting Data...3345395557</v>
         <stp/>
         <stp>BDP|1377186698529462809</stp>
         <tr r="I75" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A N/A</v>
-        <stp/>
-        <stp>BDH|1928780872019042065</stp>
-        <tr r="K3" s="1"/>
-      </tp>
-      <tp t="s">
-        <v>#N/A Requesting Data...2330350238</v>
+        <v>#N/A Requesting Data...4229603687</v>
         <stp/>
         <stp>BDP|5083165645249889039</stp>
         <tr r="C91" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3942818857</v>
+        <v>#N/A Requesting Data...3540393356</v>
         <stp/>
         <stp>BDP|4536059193783666790</stp>
         <tr r="C135" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3597557928</v>
+        <v>#N/A Requesting Data...4037373440</v>
         <stp/>
         <stp>BDP|1058017446765192947</stp>
         <tr r="W15" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3868496070</v>
+        <v>#N/A Requesting Data...3487286149</v>
         <stp/>
         <stp>BDP|4749656183205678650</stp>
         <tr r="C38" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3957371331</v>
+        <v>#N/A Requesting Data...4286569579</v>
         <stp/>
         <stp>BDP|8594765946847731528</stp>
         <tr r="I16" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3816045867</v>
+        <v>#N/A Requesting Data...4004459417</v>
         <stp/>
         <stp>BDP|9272224747107497120</stp>
         <tr r="I54" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2857712296</v>
+        <v>#N/A Requesting Data...3885529653</v>
         <stp/>
         <stp>BDP|1041774784140013721</stp>
         <tr r="C64" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3844679912</v>
+        <v>#N/A Requesting Data...4283372311</v>
         <stp/>
         <stp>BDP|1031635446673217915</stp>
         <tr r="I50" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3278825620</v>
+        <v>#N/A Requesting Data...4052962446</v>
         <stp/>
         <stp>BDP|9518744973899580904</stp>
         <tr r="C54" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1980003713</v>
+        <v>#N/A Requesting Data...4166920737</v>
         <stp/>
         <stp>BDP|5406820151140268124</stp>
         <tr r="I63" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3590148727</v>
+        <v>#N/A Requesting Data...3541653716</v>
         <stp/>
         <stp>BDP|1694830350593957686</stp>
         <tr r="I62" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3860207447</v>
+        <v>#N/A Requesting Data...3923246754</v>
         <stp/>
         <stp>BDP|7500666667194702990</stp>
         <tr r="C66" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3906609083</v>
+        <v>#N/A Requesting Data...3755275352</v>
         <stp/>
         <stp>BDP|3833953673663160479</stp>
         <tr r="C69" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2189826928</v>
+        <v>#N/A Requesting Data...4156866728</v>
         <stp/>
         <stp>BDP|9567701714471945402</stp>
         <tr r="I20" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2805831966</v>
+        <v>#N/A Requesting Data...3358707856</v>
         <stp/>
         <stp>BDP|6985157280997075252</stp>
         <tr r="C53" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2839812448</v>
+        <v>#N/A Requesting Data...3725484193</v>
         <stp/>
         <stp>BDP|2456785810019057752</stp>
         <tr r="C99" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2492231010</v>
+        <v>#N/A Requesting Data...4293395623</v>
         <stp/>
         <stp>BDP|9838492126827038280</stp>
         <tr r="C8" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3372322538</v>
+        <v>#N/A Requesting Data...3427994961</v>
         <stp/>
         <stp>BDP|8937076405480531228</stp>
         <tr r="I44" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2132057435</v>
+        <v>#N/A Requesting Data...4278352729</v>
         <stp/>
         <stp>BDP|7712524477676613982</stp>
         <tr r="I57" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2306787797</v>
+        <v>#N/A Requesting Data...3911900680</v>
         <stp/>
         <stp>BDP|1719299799386153607</stp>
         <tr r="AK7" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3688279456</v>
+        <v>#N/A Requesting Data...3621576308</v>
         <stp/>
         <stp>BDP|1429354032568056352</stp>
         <tr r="C24" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2014779700</v>
+        <v>#N/A Requesting Data...4157179162</v>
         <stp/>
         <stp>BDP|8014457710991160601</stp>
         <tr r="I28" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2608679417</v>
+        <v>#N/A Requesting Data...3915723871</v>
         <stp/>
         <stp>BDP|3033880618804365593</stp>
         <tr r="C121" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2218831786</v>
+        <v>#N/A Requesting Data...3531942492</v>
         <stp/>
         <stp>BDP|1706011192993813054</stp>
         <tr r="C96" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3902673546</v>
+        <v>#N/A Requesting Data...3997013472</v>
         <stp/>
         <stp>BDP|4435771694765996413</stp>
         <tr r="C83" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3995768507</v>
+        <v>#N/A Requesting Data...3557050187</v>
         <stp/>
         <stp>BDP|8140233211939841992</stp>
         <tr r="AK6" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1860865594</v>
+        <v>#N/A Requesting Data...3862547697</v>
         <stp/>
         <stp>BDP|1861014768014580864</stp>
         <tr r="C89" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4154094432</v>
+        <v>#N/A Requesting Data...3789195500</v>
         <stp/>
         <stp>BDP|7491589793132824247</stp>
         <tr r="AE9" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3249376567</v>
+        <v>#N/A Requesting Data...3922116320</v>
         <stp/>
         <stp>BDP|8239565527673146722</stp>
         <tr r="C144" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2191544811</v>
+        <v>#N/A Requesting Data...3540830351</v>
         <stp/>
         <stp>BDP|8403458650990508239</stp>
         <tr r="C59" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3632365611</v>
+        <v>#N/A Requesting Data...3649071298</v>
         <stp/>
         <stp>BDP|9839159273063333794</stp>
         <tr r="C29" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2313851979</v>
+        <v>#N/A Requesting Data...3426654219</v>
         <stp/>
         <stp>BDP|6567984001629018265</stp>
         <tr r="C162" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3709742789</v>
+        <v>#N/A Requesting Data...3659046908</v>
         <stp/>
         <stp>BDP|1818082544567658696</stp>
         <tr r="I36" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2701236434</v>
+        <v>#N/A Requesting Data...3992415602</v>
         <stp/>
         <stp>BDP|6993846849007577980</stp>
         <tr r="I43" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2634252600</v>
+        <v>#N/A Requesting Data...3722369113</v>
         <stp/>
         <stp>BDP|4351081083971715968</stp>
         <tr r="C68" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2835094208</v>
+        <v>#N/A Requesting Data...3886133536</v>
         <stp/>
         <stp>BDP|1704371763125928545</stp>
         <tr r="C43" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2766958322</v>
+        <v>#N/A Requesting Data...4278398681</v>
         <stp/>
         <stp>BDP|2814041733612431765</stp>
         <tr r="C105" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1866084703</v>
+        <v>#N/A Requesting Data...3999608271</v>
         <stp/>
         <stp>BDP|7829998593746821592</stp>
         <tr r="C102" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1977967483</v>
+        <v>#N/A Requesting Data...4233738968</v>
         <stp/>
         <stp>BDP|6258056741615792371</stp>
         <tr r="C106" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1907974004</v>
+        <v>#N/A Requesting Data...3678290984</v>
         <stp/>
         <stp>BDP|4617042838635235721</stp>
         <tr r="C152" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3221394326</v>
+        <v>#N/A Requesting Data...3399705159</v>
         <stp/>
         <stp>BDP|1240404019180728146</stp>
         <tr r="C65" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3260218647</v>
+        <v>#N/A Requesting Data...3729413411</v>
         <stp/>
         <stp>BDP|2330938495090261788</stp>
         <tr r="AK8" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2596751629</v>
+        <v>#N/A Requesting Data...3633898979</v>
         <stp/>
         <stp>BDP|8465946647526914636</stp>
         <tr r="I42" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4174684462</v>
+        <v>#N/A Requesting Data...3751265304</v>
         <stp/>
         <stp>BDP|9950496650399002439</stp>
         <tr r="C123" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3040604761</v>
+        <v>#N/A Requesting Data...3416375451</v>
         <stp/>
         <stp>BDP|2667683450453794790</stp>
         <tr r="C115" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2701293268</v>
+        <v>#N/A Requesting Data...4233959654</v>
         <stp/>
         <stp>BDP|7273482579447089634</stp>
         <tr r="I10" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3589535068</v>
+        <v>#N/A Requesting Data...3596686365</v>
         <stp/>
         <stp>BDP|5025328525011211047</stp>
         <tr r="C34" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3794355669</v>
+        <v>#N/A Requesting Data...3892181665</v>
         <stp/>
         <stp>BDP|3834658410891383085</stp>
         <tr r="C9" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2555278291</v>
+        <v>#N/A Requesting Data...3729004745</v>
         <stp/>
         <stp>BDP|5204453854055475411</stp>
         <tr r="C72" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2790422120</v>
+        <v>#N/A Requesting Data...3978935529</v>
         <stp/>
         <stp>BDP|4788424420704423360</stp>
         <tr r="W5" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2470929154</v>
+        <v>#N/A Requesting Data...3771864909</v>
         <stp/>
         <stp>BDP|7184509443593036063</stp>
         <tr r="I18" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2987892223</v>
+        <v>#N/A Requesting Data...4072490493</v>
         <stp/>
         <stp>BDP|4409571100871585532</stp>
         <tr r="AF4" s="1"/>
         <tr r="C73" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3011657820</v>
+        <v>#N/A Requesting Data...4022636152</v>
         <stp/>
         <stp>BDP|9147095673928589078</stp>
         <tr r="I24" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3010194367</v>
+        <v>#N/A Requesting Data...4139437741</v>
         <stp/>
         <stp>BDP|6751685416204293341</stp>
         <tr r="C159" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2380126017</v>
+        <v>#N/A Requesting Data...3630886140</v>
         <stp/>
         <stp>BDP|2646981305435776837</stp>
         <tr r="I38" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3609990263</v>
+        <v>#N/A Requesting Data...4202048781</v>
         <stp/>
         <stp>BDP|5538226760447497012</stp>
         <tr r="I15" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4208334264</v>
+        <v>#N/A Requesting Data...3433319543</v>
         <stp/>
         <stp>BDP|4410242283930284836</stp>
         <tr r="C108" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4035478997</v>
+        <v>#N/A Requesting Data...3825464004</v>
         <stp/>
         <stp>BDP|5599646844690725120</stp>
         <tr r="V7" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2829535929</v>
+        <v>#N/A Requesting Data...4189717978</v>
         <stp/>
         <stp>BDP|7323562495194409926</stp>
         <tr r="AE8" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3264035869</v>
+        <v>#N/A Requesting Data...3811004637</v>
         <stp/>
         <stp>BDP|4433046404986412449</stp>
         <tr r="C158" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3312136990</v>
+        <v>#N/A Requesting Data...4103615746</v>
         <stp/>
         <stp>BDP|2382374971599643898</stp>
         <tr r="C26" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3451448050</v>
+        <v>#N/A Requesting Data...4251956510</v>
         <stp/>
         <stp>BDP|5510498631210704517</stp>
         <tr r="AF14" s="1"/>
         <tr r="C84" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3066656999</v>
+        <v>#N/A Requesting Data...3960491759</v>
         <stp/>
         <stp>BDP|9026898305143148551</stp>
         <tr r="V6" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2201713113</v>
+        <v>#N/A Requesting Data...3622289166</v>
         <stp/>
         <stp>BDP|7449967289015704458</stp>
         <tr r="I34" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1978872656</v>
+        <v>#N/A Requesting Data...3818967470</v>
         <stp/>
         <stp>BDP|7128217049024788278</stp>
         <tr r="C126" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3462485681</v>
+        <v>#N/A Requesting Data...4137280942</v>
         <stp/>
         <stp>BDP|1225789237812079036</stp>
         <tr r="AK13" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1946002533</v>
+        <v>#N/A Requesting Data...4040382327</v>
         <stp/>
         <stp>BDP|2688398335815461032</stp>
         <tr r="I72" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4235038550</v>
+        <v>#N/A Requesting Data...3514838100</v>
         <stp/>
         <stp>BDP|5407744553420709092</stp>
         <tr r="I45" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2427692396</v>
+        <v>#N/A Requesting Data...3903027999</v>
         <stp/>
         <stp>BDP|3301994951851485995</stp>
         <tr r="C103" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4203364516</v>
+        <v>#N/A Requesting Data...3645214543</v>
         <stp/>
         <stp>BDP|1715692313415242487</stp>
         <tr r="AE10" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3478381088</v>
+        <v>#N/A Requesting Data...3992425772</v>
         <stp/>
         <stp>BDP|7787511640980270100</stp>
         <tr r="C19" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3041044922</v>
+        <v>#N/A Requesting Data...3870734717</v>
         <stp/>
         <stp>BDP|5881769373931552438</stp>
         <tr r="C37" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3979539860</v>
+        <v>#N/A Requesting Data...3688028141</v>
         <stp/>
         <stp>BDP|8775887083928455015</stp>
         <tr r="I65" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2304731951</v>
+        <v>#N/A Requesting Data...3453095768</v>
         <stp/>
         <stp>BDP|2999354362923182419</stp>
         <tr r="C119" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2984894505</v>
+        <v>#N/A Requesting Data...4095344397</v>
         <stp/>
         <stp>BDP|7144957155592866969</stp>
         <tr r="I7" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2238903263</v>
+        <v>#N/A Requesting Data...3549583395</v>
         <stp/>
         <stp>BDP|7376321538937352077</stp>
         <tr r="I31" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3639886418</v>
+        <v>#N/A Requesting Data...3905415378</v>
         <stp/>
         <stp>BDP|6067526931230468040</stp>
         <tr r="C41" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2646798338</v>
+        <v>#N/A Requesting Data...4101122898</v>
         <stp/>
         <stp>BDP|4583763296699195352</stp>
         <tr r="C90" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3598830917</v>
+        <v>#N/A Requesting Data...3796480950</v>
         <stp/>
         <stp>BDP|9013230294690428273</stp>
         <tr r="V12" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3267410995</v>
+        <v>#N/A Requesting Data...4115120076</v>
         <stp/>
         <stp>BDP|2884216262693648467</stp>
         <tr r="C101" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1990406057</v>
+        <v>#N/A Requesting Data...3772517432</v>
         <stp/>
         <stp>BDP|6653931085044954226</stp>
         <tr r="C49" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3034322624</v>
+        <v>#N/A Requesting Data...3544973112</v>
         <stp/>
         <stp>BDP|8816274015493202973</stp>
         <tr r="AE17" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2601480253</v>
+        <v>#N/A Requesting Data...4237629109</v>
         <stp/>
         <stp>BDP|4442406327391170217</stp>
         <tr r="I69" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3740624920</v>
+        <v>#N/A Requesting Data...3499000665</v>
         <stp/>
         <stp>BDP|2160522543402219031</stp>
         <tr r="C44" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4257420180</v>
+        <v>#N/A Requesting Data...3550659785</v>
         <stp/>
         <stp>BDP|8134386539959622001</stp>
         <tr r="I12" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4152688725</v>
+        <v>#N/A Requesting Data...3521517567</v>
         <stp/>
         <stp>BDP|5175596859875743108</stp>
         <tr r="C160" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3055398047</v>
+        <v>#N/A Requesting Data...4273262099</v>
         <stp/>
         <stp>BDP|6213448269441194717</stp>
         <tr r="I33" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2712553546</v>
+        <v>#N/A Requesting Data...4119074534</v>
         <stp/>
         <stp>BDP|9203340293449607800</stp>
         <tr r="W4" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2437002915</v>
+        <v>#N/A Requesting Data...3873981532</v>
         <stp/>
         <stp>BDP|1674630257287785748</stp>
         <tr r="C21" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3074447044</v>
+        <v>#N/A Requesting Data...4050735674</v>
         <stp/>
         <stp>BDP|6722538765332235541</stp>
         <tr r="I79" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2848948934</v>
+        <v>#N/A Requesting Data...3643172788</v>
         <stp/>
         <stp>BDP|4321930751773162948</stp>
         <tr r="C143" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2362402499</v>
+        <v>#N/A Requesting Data...3989199330</v>
         <stp/>
         <stp>BDP|2465770666370232132</stp>
         <tr r="AF12" s="1"/>
         <tr r="C81" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3353025422</v>
+        <v>#N/A Requesting Data...3882995760</v>
         <stp/>
         <stp>BDP|3614236909801232351</stp>
         <tr r="AF10" s="1"/>
         <tr r="C79" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2790290660</v>
+        <v>#N/A Requesting Data...4262421920</v>
         <stp/>
         <stp>BDP|9264525602047863819</stp>
         <tr r="C129" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3323650869</v>
+        <v>#N/A Requesting Data...4176325929</v>
         <stp/>
         <stp>BDP|3022564266265232698</stp>
         <tr r="C22" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2611102992</v>
+        <v>#N/A Requesting Data...4062548016</v>
         <stp/>
         <stp>BDP|3065289322003110341</stp>
         <tr r="C17" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2951793352</v>
+        <v>#N/A Requesting Data...4267650008</v>
         <stp/>
         <stp>BDP|3488562983458433575</stp>
         <tr r="C97" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4261613614</v>
+        <v>#N/A Requesting Data...3730141989</v>
         <stp/>
         <stp>BDP|8883686451619078120</stp>
         <tr r="I78" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3779344500</v>
+        <v>#N/A Requesting Data...4212036433</v>
         <stp/>
         <stp>BDP|3169607923705567144</stp>
         <tr r="AE12" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4067549513</v>
+        <v>#N/A Requesting Data...3559291324</v>
         <stp/>
         <stp>BDP|5066211127374524238</stp>
         <tr r="C23" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3020386381</v>
+        <v>#N/A Requesting Data...4210310501</v>
         <stp/>
         <stp>BDP|4981558656002856539</stp>
         <tr r="AF7" s="1"/>
         <tr r="C76" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4157995243</v>
+        <v>#N/A Requesting Data...3607021117</v>
         <stp/>
         <stp>BDP|1175608250980429144</stp>
         <tr r="AK11" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2561876667</v>
+        <v>#N/A Requesting Data...3853740636</v>
         <stp/>
         <stp>BDP|4365340775557570411</stp>
         <tr r="C161" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2361314268</v>
+        <v>#N/A Requesting Data...3970107078</v>
         <stp/>
         <stp>BDP|1345751232810291632</stp>
         <tr r="C57" s="3"/>
@@ -3781,109 +3782,109 @@
         <tr r="T5" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2667157386</v>
+        <v>#N/A Requesting Data...3937981670</v>
         <stp/>
         <stp>BDP|531173126430871456</stp>
         <tr r="AE13" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2889190828</v>
+        <v>#N/A Requesting Data...4171849972</v>
         <stp/>
         <stp>BDP|437360509784535044</stp>
         <tr r="C28" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3721103700</v>
+        <v>#N/A Requesting Data...3685806614</v>
         <stp/>
         <stp>BDP|719920997835819372</stp>
         <tr r="I21" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3206677458</v>
+        <v>#N/A Requesting Data...4117301647</v>
         <stp/>
         <stp>BDP|220158664486763756</stp>
         <tr r="I68" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1986341813</v>
+        <v>#N/A Requesting Data...3851677367</v>
         <stp/>
         <stp>BDP|327790706290079409</stp>
         <tr r="C62" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2944081823</v>
+        <v>#N/A Requesting Data...4003714121</v>
         <stp/>
         <stp>BDP|598255408960214169</stp>
         <tr r="AK14" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2048130234</v>
+        <v>#N/A Requesting Data...3702356949</v>
         <stp/>
         <stp>BDP|752544571119749831</stp>
         <tr r="I74" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3448278637</v>
+        <v>#N/A Requesting Data...4234505351</v>
         <stp/>
         <stp>BDP|314325233504172733</stp>
         <tr r="C3" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3501454942</v>
+        <v>#N/A Requesting Data...4066518155</v>
         <stp/>
         <stp>BDP|535673656531239152</stp>
         <tr r="C14" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3935314469</v>
+        <v>#N/A Requesting Data...3705266861</v>
         <stp/>
         <stp>BDP|215538495568786816</stp>
         <tr r="C67" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4262181170</v>
+        <v>#N/A Requesting Data...3759256984</v>
         <stp/>
         <stp>BDP|165287045318738295</stp>
         <tr r="I61" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2439304493</v>
+        <v>#N/A Requesting Data...4009593494</v>
         <stp/>
         <stp>BDP|760657431968210265</stp>
         <tr r="I58" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2817591033</v>
+        <v>#N/A Requesting Data...3893089100</v>
         <stp/>
         <stp>BDP|116642544894402895</stp>
         <tr r="W11" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3071415255</v>
+        <v>#N/A Requesting Data...4053065170</v>
         <stp/>
         <stp>BDP|379626236869393287</stp>
         <tr r="I77" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3670125676</v>
+        <v>#N/A Requesting Data...4120897374</v>
         <stp/>
         <stp>BDP|408866569944722468</stp>
         <tr r="AK15" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3615187807</v>
+        <v>#N/A Requesting Data...3877673936</v>
         <stp/>
         <stp>BDP|890144082077292780</stp>
         <tr r="I19" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2949840094</v>
+        <v>#N/A Requesting Data...4224486081</v>
         <stp/>
         <stp>BDP|390385784833233012</stp>
         <tr r="AK9" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3063355595</v>
+        <v>#N/A Requesting Data...3916391867</v>
         <stp/>
         <stp>BDP|487608147160746983</stp>
         <tr r="I2" s="3"/>
@@ -3905,13 +3906,13 @@
         <tr r="T14" s="1"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3735120232</v>
+        <v>#N/A Requesting Data...4119485677</v>
         <stp/>
         <stp>BDP|930696567893770943</stp>
         <tr r="C55" s="3"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2977334576</v>
+        <v>#N/A Requesting Data...4093492815</v>
         <stp/>
         <stp>BDP|267021441459137755</stp>
         <tr r="I55" s="3"/>
@@ -4017,103 +4018,103 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>5.3752557610911023E-3</c:v>
+                  <c:v>9.347016065999858E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.1688489100415449E-3</c:v>
+                  <c:v>5.3504580358290088E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.4023300559075524E-2</c:v>
+                  <c:v>1.5863009703026787E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9799693437420718E-2</c:v>
+                  <c:v>2.1017811453843738E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.0927948543443708E-2</c:v>
+                  <c:v>2.1983983432336762E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.1763258488800119E-2</c:v>
+                  <c:v>2.2587393864522687E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.2334247377854055E-2</c:v>
+                  <c:v>2.299319229659158E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.2745377323947213E-2</c:v>
+                  <c:v>2.3314760502477494E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.304792263276112E-2</c:v>
+                  <c:v>2.3562203323119091E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.3272408254412014E-2</c:v>
+                  <c:v>2.3742478784605003E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.3440316380464621E-2</c:v>
+                  <c:v>2.3874396466057712E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.357725549259837E-2</c:v>
+                  <c:v>2.398286557724516E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.3679988093457727E-2</c:v>
+                  <c:v>2.4061402775475305E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.3756001767544221E-2</c:v>
+                  <c:v>2.4116583276562631E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.3817544490837284E-2</c:v>
+                  <c:v>2.4165809623944989E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.3872734759779135E-2</c:v>
+                  <c:v>2.4218334864596125E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.3911674765301871E-2</c:v>
+                  <c:v>2.4254680613017721E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.3937193187117956E-2</c:v>
+                  <c:v>2.4277668356428528E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.3953843594760826E-2</c:v>
+                  <c:v>2.4289821731264816E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.3961765633969678E-2</c:v>
+                  <c:v>2.4292697181691691E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.3961398687502689E-2</c:v>
+                  <c:v>2.4287616426593939E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.3954381768301447E-2</c:v>
+                  <c:v>2.4276212948929565E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.3950755095908827E-2</c:v>
+                  <c:v>2.4265707288241956E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.3940967412554803E-2</c:v>
+                  <c:v>2.4249524394082345E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.3925837383968362E-2</c:v>
+                  <c:v>2.4228426613449594E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.3912513610706343E-2</c:v>
+                  <c:v>2.4211288471696513E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.3904233092381766E-2</c:v>
+                  <c:v>2.4201047367280015E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.3891087364454666E-2</c:v>
+                  <c:v>2.4185967377987172E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.3873646641830559E-2</c:v>
+                  <c:v>2.4166618105361914E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.3869412529679224E-2</c:v>
+                  <c:v>2.415825840118746E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.3866245289101862E-2</c:v>
+                  <c:v>2.414989809438195E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.3858468792947507E-2</c:v>
+                  <c:v>2.4137200739015263E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.3849262340472244E-2</c:v>
+                  <c:v>2.4123934672108716E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5809,43 +5810,23 @@
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="G2" s="20">
-        <v>46223</v>
-      </c>
-      <c r="H2">
-        <v>334.30894000000001</v>
-      </c>
-      <c r="I2" s="26">
-        <f t="shared" ref="I2:I4" ca="1" si="0">IF((G2=$C$20),$D$20,0)</f>
-        <v>334.30893548387098</v>
-      </c>
       <c r="K2" t="s">
         <v>572</v>
       </c>
       <c r="L2" t="s">
         <v>0</v>
       </c>
-      <c r="Z2" s="38">
+      <c r="Z2" s="37">
         <f ca="1">MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate)-2,1))</f>
         <v>5</v>
       </c>
-      <c r="AA2" s="39">
+      <c r="AA2" s="38">
         <f ca="1">IF(DAY(strippingDate)&gt;=15,2,1)</f>
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="D3" s="2"/>
-      <c r="G3" s="20">
-        <v>46220</v>
-      </c>
-      <c r="H3">
-        <v>334.10541999999998</v>
-      </c>
-      <c r="I3" s="26">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
       <c r="K3" s="2" cm="1">
         <f t="array" aca="1" ref="K3:L26" ca="1">_xll.BDH("CPURNSA Index","PX_LAST",DATE(YEAR(D10),MONTH(D10)-25,21),D10,"Dir=V","Dts=S","Sort=D",CONCATENATE("Per=c",D13),"DtFmt=D","UseDPDF=Y")</f>
         <v>46203</v>
@@ -5873,8 +5854,8 @@
       <c r="W3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="40"/>
-      <c r="AA3" s="41"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="40"/>
       <c r="AC3" s="10" t="s">
         <v>5</v>
       </c>
@@ -5899,16 +5880,6 @@
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="D4" s="2"/>
-      <c r="G4" s="20">
-        <v>46219</v>
-      </c>
-      <c r="H4" s="27">
-        <v>334.03758064516097</v>
-      </c>
-      <c r="I4" s="26">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
       <c r="J4" s="26"/>
       <c r="K4" s="2">
         <f ca="1"/>
@@ -5935,7 +5906,7 @@
         <f>DATEVALUE(_xll.BDP(Q4, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="36" cm="1">
+      <c r="U4" s="12" cm="1">
         <f t="array" ref="U4">_xll.qwCalAddMonths("All",V4,-3)</f>
         <v>46204</v>
       </c>
@@ -5945,14 +5916,14 @@
       </c>
       <c r="W4" s="9">
         <f>_xll.BDP(Q4, "PX_MID")</f>
-        <v>333.97989999999999</v>
-      </c>
-      <c r="Z4" s="40">
+        <v>334.13659999999999</v>
+      </c>
+      <c r="Z4" s="39">
         <f ca="1">MOD($Z$2-P15+12,12)</f>
         <v>11</v>
       </c>
-      <c r="AA4" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z4+$AA$2,1)</f>
+      <c r="AA4" s="40">
+        <f t="shared" ref="AA4:AA15" ca="1" si="0">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z4+$AA$2,1)</f>
         <v>45931</v>
       </c>
       <c r="AC4" s="10" t="s">
@@ -5960,15 +5931,15 @@
       </c>
       <c r="AD4" s="13">
         <f t="shared" ref="AD4:AD17" ca="1" si="1">$D$10+2</f>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE4" s="10" t="str">
         <f>_xll.BDP(AC4, "MATURITY")</f>
-        <v>7/20/2027</v>
+        <v>7/23/2027</v>
       </c>
       <c r="AF4" s="10">
         <f>_xll.BDP(AC4, "PX_LAST")</f>
-        <v>1.9449000000000001</v>
+        <v>2.0363000000000002</v>
       </c>
       <c r="AG4" s="10">
         <v>1</v>
@@ -5981,21 +5952,12 @@
       </c>
       <c r="AK4" s="14">
         <f>_xll.BDP(AJ4, "PX_LAST")</f>
-        <v>0.996</v>
+        <v>0.99619999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="D5" s="2"/>
-      <c r="G5" s="20">
-        <v>46218</v>
-      </c>
-      <c r="H5">
-        <v>333.96974</v>
-      </c>
-      <c r="I5" s="26">
-        <f ca="1">IF((G5=$C$20),$D$20,0)</f>
-        <v>0</v>
-      </c>
+      <c r="G5" s="20"/>
       <c r="J5" s="26"/>
       <c r="K5" s="2">
         <f ca="1"/>
@@ -6022,7 +5984,7 @@
         <f>DATEVALUE(_xll.BDP(Q5, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>45962</v>
       </c>
-      <c r="U5" s="36" cm="1">
+      <c r="U5" s="12" cm="1">
         <f t="array" ref="U5">_xll.qwCalAddMonths("All",V5,-3)</f>
         <v>46235</v>
       </c>
@@ -6032,18 +5994,18 @@
       </c>
       <c r="W5" s="9">
         <f>_xll.BDP(Q5, "PX_MID")</f>
-        <v>335.11</v>
+        <v>335.50984999999997</v>
       </c>
       <c r="X5" t="b">
         <f>V5&gt;V4</f>
         <v>1</v>
       </c>
-      <c r="Z5" s="40">
-        <f ca="1">MOD($Z$2-P4+12,12)</f>
+      <c r="Z5" s="39">
+        <f t="shared" ref="Z5:Z15" ca="1" si="2">MOD($Z$2-P4+12,12)</f>
         <v>10</v>
       </c>
-      <c r="AA5" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z5+$AA$2,1)</f>
+      <c r="AA5" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>45962</v>
       </c>
       <c r="AC5" s="10" t="s">
@@ -6051,15 +6013,15 @@
       </c>
       <c r="AD5" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE5" s="10" t="str">
         <f>_xll.BDP(AC5, "MATURITY")</f>
-        <v>7/20/2028</v>
+        <v>7/23/2028</v>
       </c>
       <c r="AF5" s="10">
         <f>_xll.BDP(AC5, "PX_LAST")</f>
-        <v>2.2675000000000001</v>
+        <v>2.3210000000000002</v>
       </c>
       <c r="AG5" s="10">
         <f>AG4+1</f>
@@ -6073,21 +6035,12 @@
       </c>
       <c r="AK5" s="14">
         <f>_xll.BDP(AJ5, "PX_LAST")</f>
-        <v>0.998</v>
+        <v>0.99819999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="D6" s="20"/>
-      <c r="G6" s="20">
-        <v>46217</v>
-      </c>
-      <c r="H6">
-        <v>333.90190000000001</v>
-      </c>
-      <c r="I6" s="26">
-        <f ca="1">IF((G6=$C$20),$D$20,0)</f>
-        <v>0</v>
-      </c>
+      <c r="G6" s="20"/>
       <c r="J6" s="26"/>
       <c r="K6" s="2">
         <f ca="1"/>
@@ -6114,7 +6067,7 @@
         <f>DATEVALUE(_xll.BDP(Q6, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>45992</v>
       </c>
-      <c r="U6" s="36" cm="1">
+      <c r="U6" s="12" cm="1">
         <f t="array" ref="U6">_xll.qwCalAddMonths("All",V6,-3)</f>
         <v>46266</v>
       </c>
@@ -6124,18 +6077,18 @@
       </c>
       <c r="W6" s="9">
         <f>_xll.BDP(Q6, "PX_MID")</f>
-        <v>335.64</v>
+        <v>336.1</v>
       </c>
       <c r="X6" t="b">
-        <f t="shared" ref="X6:X15" si="2">V6&gt;V5</f>
+        <f t="shared" ref="X6:X14" si="3">V6&gt;V5</f>
         <v>1</v>
       </c>
-      <c r="Z6" s="40">
-        <f ca="1">MOD($Z$2-P5+12,12)</f>
+      <c r="Z6" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>9</v>
       </c>
-      <c r="AA6" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z6+$AA$2,1)</f>
+      <c r="AA6" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>45992</v>
       </c>
       <c r="AC6" s="10" t="s">
@@ -6143,18 +6096,18 @@
       </c>
       <c r="AD6" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE6" s="10" t="str">
         <f>_xll.BDP(AC6, "MATURITY")</f>
-        <v>7/20/2029</v>
+        <v>7/23/2029</v>
       </c>
       <c r="AF6" s="10">
         <f>_xll.BDP(AC6, "PX_LAST")</f>
-        <v>2.3567</v>
+        <v>2.3948999999999998</v>
       </c>
       <c r="AG6" s="10">
-        <f t="shared" ref="AG6:AG13" si="3">AG5+1</f>
+        <f t="shared" ref="AG6:AG13" si="4">AG5+1</f>
         <v>3</v>
       </c>
       <c r="AI6" s="14">
@@ -6165,19 +6118,19 @@
       </c>
       <c r="AK6" s="14">
         <f>_xll.BDP(AJ6, "PX_LAST")</f>
-        <v>1.0009999999999999</v>
+        <v>1.0005999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="D7" s="20"/>
       <c r="G7" s="20">
-        <v>46213</v>
+        <v>46225</v>
       </c>
       <c r="H7">
-        <v>333.63055000000003</v>
+        <v>334.44461290322579</v>
       </c>
       <c r="I7" s="26">
-        <f t="shared" ref="I7:I69" ca="1" si="4">IF((G7=$C$20),$D$20,0)</f>
+        <f ca="1">IF((G7=$C$20),$D$20,0)</f>
         <v>0</v>
       </c>
       <c r="J7" s="26"/>
@@ -6206,7 +6159,7 @@
         <f>DATEVALUE(_xll.BDP(Q7, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>46023</v>
       </c>
-      <c r="U7" s="36" cm="1">
+      <c r="U7" s="12" cm="1">
         <f t="array" ref="U7">_xll.qwCalAddMonths("All",V7,-3)</f>
         <v>46296</v>
       </c>
@@ -6216,18 +6169,18 @@
       </c>
       <c r="W7" s="9">
         <f>_xll.BDP(Q7, "PX_MID")</f>
-        <v>335.51004999999998</v>
+        <v>335.96985000000001</v>
       </c>
       <c r="X7" t="b">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Z7" s="40">
-        <f ca="1">MOD($Z$2-P6+12,12)</f>
+      <c r="Z7" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>8</v>
       </c>
-      <c r="AA7" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z7+$AA$2,1)</f>
+      <c r="AA7" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>46023</v>
       </c>
       <c r="AC7" s="10" t="s">
@@ -6235,18 +6188,18 @@
       </c>
       <c r="AD7" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE7" s="10" t="str">
         <f>_xll.BDP(AC7, "MATURITY")</f>
-        <v>7/20/2030</v>
+        <v>7/23/2030</v>
       </c>
       <c r="AF7" s="10">
         <f>_xll.BDP(AC7, "PX_LAST")</f>
-        <v>2.3889999999999998</v>
+        <v>2.42</v>
       </c>
       <c r="AG7" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="AI7" s="14">
@@ -6257,18 +6210,18 @@
       </c>
       <c r="AK7" s="14">
         <f>_xll.BDP(AJ7, "PX_LAST")</f>
-        <v>1.0029999999999999</v>
+        <v>1.0023</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="G8" s="20">
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="H8">
-        <v>333.56270999999998</v>
+        <v>334.37677419354839</v>
       </c>
       <c r="I8" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF((G8=$C$20),$D$20,0)</f>
         <v>0</v>
       </c>
       <c r="J8" s="26"/>
@@ -6297,7 +6250,7 @@
         <f>DATEVALUE(_xll.BDP(Q8, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>46054</v>
       </c>
-      <c r="U8" s="36" cm="1">
+      <c r="U8" s="12" cm="1">
         <f t="array" ref="U8">_xll.qwCalAddMonths("All",V8,-3)</f>
         <v>46327</v>
       </c>
@@ -6307,18 +6260,18 @@
       </c>
       <c r="W8" s="9">
         <f>_xll.BDP(Q8, "PX_MID")</f>
-        <v>335.08994999999999</v>
+        <v>335.50990000000002</v>
       </c>
       <c r="X8" t="b">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Z8" s="40">
-        <f ca="1">MOD($Z$2-P7+12,12)</f>
+      <c r="Z8" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>7</v>
       </c>
-      <c r="AA8" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z8+$AA$2,1)</f>
+      <c r="AA8" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>46054</v>
       </c>
       <c r="AC8" s="10" t="s">
@@ -6326,18 +6279,18 @@
       </c>
       <c r="AD8" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE8" s="10" t="str">
         <f>_xll.BDP(AC8, "MATURITY")</f>
-        <v>7/20/2031</v>
+        <v>7/23/2031</v>
       </c>
       <c r="AF8" s="17">
         <f>_xll.BDP(AC8, "PX_LAST")</f>
-        <v>2.4020000000000001</v>
+        <v>2.4329000000000001</v>
       </c>
       <c r="AG8" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="AI8" s="14">
@@ -6354,13 +6307,13 @@
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="D9" s="1"/>
       <c r="G9" s="20">
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="H9">
-        <v>333.49486999999999</v>
+        <v>334.30894000000001</v>
       </c>
       <c r="I9" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ref="I9:I72" ca="1" si="5">IF((G9=$C$20),$D$20,0)</f>
         <v>0</v>
       </c>
       <c r="J9" s="26"/>
@@ -6399,18 +6352,18 @@
       </c>
       <c r="W9" s="9">
         <f>_xll.BDP(Q9, "PX_MID")</f>
-        <v>335.06995000000001</v>
+        <v>335.46985000000001</v>
       </c>
       <c r="X9" t="b">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Z9" s="40">
-        <f ca="1">MOD($Z$2-P8+12,12)</f>
+      <c r="Z9" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>6</v>
       </c>
-      <c r="AA9" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z9+$AA$2,1)</f>
+      <c r="AA9" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>46082</v>
       </c>
       <c r="AC9" s="10" t="s">
@@ -6418,18 +6371,18 @@
       </c>
       <c r="AD9" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE9" s="10" t="str">
         <f>_xll.BDP(AC9, "MATURITY")</f>
-        <v>7/20/2032</v>
+        <v>7/23/2032</v>
       </c>
       <c r="AF9" s="10">
         <f>_xll.BDP(AC9, "PX_LAST")</f>
-        <v>2.403</v>
+        <v>2.4327000000000001</v>
       </c>
       <c r="AG9" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AI9" s="14">
@@ -6440,7 +6393,7 @@
       </c>
       <c r="AK9" s="14">
         <f>_xll.BDP(AJ9, "PX_LAST")</f>
-        <v>1.0029999999999999</v>
+        <v>1.0028999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.25">
@@ -6449,16 +6402,16 @@
       </c>
       <c r="D10" s="20">
         <f ca="1">TODAY()-A1</f>
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="G10" s="20">
-        <v>46210</v>
+        <v>46220</v>
       </c>
       <c r="H10">
-        <v>333.42703</v>
+        <v>334.10541999999998</v>
       </c>
       <c r="I10" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J10" s="26"/>
@@ -6487,7 +6440,7 @@
         <f>DATEVALUE(_xll.BDP(Q10, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>46113</v>
       </c>
-      <c r="U10" s="36" cm="1">
+      <c r="U10" s="12" cm="1">
         <f t="array" ref="U10">_xll.qwCalAddMonths("All",V10,-3)</f>
         <v>46388</v>
       </c>
@@ -6497,18 +6450,18 @@
       </c>
       <c r="W10" s="9">
         <f>_xll.BDP(Q10, "PX_MID")</f>
-        <v>336.42005</v>
+        <v>336.84994999999998</v>
       </c>
       <c r="X10" t="b">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Z10" s="40">
-        <f ca="1">MOD($Z$2-P9+12,12)</f>
+      <c r="Z10" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>5</v>
       </c>
-      <c r="AA10" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z10+$AA$2,1)</f>
+      <c r="AA10" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>46113</v>
       </c>
       <c r="AC10" s="10" t="s">
@@ -6516,18 +6469,18 @@
       </c>
       <c r="AD10" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE10" s="10" t="str">
         <f>_xll.BDP(AC10, "MATURITY")</f>
-        <v>7/20/2033</v>
+        <v>7/23/2033</v>
       </c>
       <c r="AF10" s="10">
         <f>_xll.BDP(AC10, "PX_LAST")</f>
-        <v>2.3978999999999999</v>
+        <v>2.4257</v>
       </c>
       <c r="AG10" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="AI10" s="14">
@@ -6538,7 +6491,7 @@
       </c>
       <c r="AK10" s="14">
         <f>_xll.BDP(AJ10, "PX_LAST")</f>
-        <v>1.002</v>
+        <v>1.0021</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
@@ -6547,16 +6500,16 @@
       </c>
       <c r="D11" s="20" cm="1">
         <f t="array" aca="1" ref="D11" ca="1">_xll.qwCalAddBusDays("US",strippingDate,2)</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="G11" s="20">
-        <v>46209</v>
-      </c>
-      <c r="H11">
-        <v>333.35919000000001</v>
+        <v>46219</v>
+      </c>
+      <c r="H11" s="27">
+        <v>334.03758064516097</v>
       </c>
       <c r="I11" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J11" s="26"/>
@@ -6585,7 +6538,7 @@
         <f>DATEVALUE(_xll.BDP(Q11, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>46143</v>
       </c>
-      <c r="U11" s="36" cm="1">
+      <c r="U11" s="12" cm="1">
         <f t="array" ref="U11">_xll.qwCalAddMonths("All",V11,-3)</f>
         <v>46419</v>
       </c>
@@ -6595,18 +6548,18 @@
       </c>
       <c r="W11" s="9">
         <f>_xll.BDP(Q11, "PX_MID")</f>
-        <v>337.69</v>
+        <v>338.11984999999999</v>
       </c>
       <c r="X11" t="b">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Z11" s="40">
-        <f ca="1">MOD($Z$2-P10+12,12)</f>
+      <c r="Z11" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>4</v>
       </c>
-      <c r="AA11" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z11+$AA$2,1)</f>
+      <c r="AA11" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>46143</v>
       </c>
       <c r="AC11" s="10" t="s">
@@ -6614,18 +6567,18 @@
       </c>
       <c r="AD11" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE11" s="10" t="str">
         <f>_xll.BDP(AC11, "MATURITY")</f>
-        <v>7/20/2034</v>
+        <v>7/23/2034</v>
       </c>
       <c r="AF11" s="10">
         <f>_xll.BDP(AC11, "PX_LAST")</f>
-        <v>2.3925000000000001</v>
+        <v>2.4199000000000002</v>
       </c>
       <c r="AG11" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="AI11" s="14">
@@ -6636,7 +6589,7 @@
       </c>
       <c r="AK11" s="14">
         <f>_xll.BDP(AJ11, "PX_LAST")</f>
-        <v>1.002</v>
+        <v>1.0018</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.25">
@@ -6648,13 +6601,13 @@
         <v>46142</v>
       </c>
       <c r="G12" s="20">
-        <v>46205</v>
+        <v>46218</v>
       </c>
       <c r="H12">
-        <v>333.08784000000003</v>
+        <v>333.96974</v>
       </c>
       <c r="I12" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J12" s="26"/>
@@ -6683,7 +6636,7 @@
         <f>DATEVALUE(_xll.BDP(Q12, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>46174</v>
       </c>
-      <c r="U12" s="36" cm="1">
+      <c r="U12" s="12" cm="1">
         <f t="array" ref="U12">_xll.qwCalAddMonths("All",V12,-3)</f>
         <v>46447</v>
       </c>
@@ -6693,18 +6646,18 @@
       </c>
       <c r="W12" s="9">
         <f>_xll.BDP(Q12, "PX_MID")</f>
-        <v>339.05860000000001</v>
+        <v>339.58994999999999</v>
       </c>
       <c r="X12" t="b">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Z12" s="40">
-        <f ca="1">MOD($Z$2-P11+12,12)</f>
+      <c r="Z12" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>3</v>
       </c>
-      <c r="AA12" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z12+$AA$2,1)</f>
+      <c r="AA12" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>46174</v>
       </c>
       <c r="AC12" s="10" t="s">
@@ -6712,18 +6665,18 @@
       </c>
       <c r="AD12" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE12" s="10" t="str">
         <f>_xll.BDP(AC12, "MATURITY")</f>
-        <v>7/20/2035</v>
+        <v>7/23/2035</v>
       </c>
       <c r="AF12" s="10">
         <f>_xll.BDP(AC12, "PX_LAST")</f>
-        <v>2.3898000000000001</v>
+        <v>2.4156</v>
       </c>
       <c r="AG12" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="AI12" s="14">
@@ -6734,7 +6687,7 @@
       </c>
       <c r="AK12" s="14">
         <f>_xll.BDP(AJ12, "PX_LAST")</f>
-        <v>1.002</v>
+        <v>1.0015000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.25">
@@ -6745,13 +6698,13 @@
         <v>33</v>
       </c>
       <c r="G13" s="20">
-        <v>46204</v>
+        <v>46217</v>
       </c>
       <c r="H13">
-        <v>333.02</v>
+        <v>333.90190000000001</v>
       </c>
       <c r="I13" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J13" s="26"/>
@@ -6780,7 +6733,7 @@
         <f>DATEVALUE(_xll.BDP(Q13, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>46204</v>
       </c>
-      <c r="U13" s="36" cm="1">
+      <c r="U13" s="12" cm="1">
         <f t="array" ref="U13">_xll.qwCalAddMonths("All",V13,-3)</f>
         <v>46478</v>
       </c>
@@ -6790,18 +6743,18 @@
       </c>
       <c r="W13" s="9">
         <f>_xll.BDP(Q13, "PX_MID")</f>
-        <v>340.18405000000001</v>
+        <v>340.64</v>
       </c>
       <c r="X13" t="b">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Z13" s="40">
-        <f ca="1">MOD($Z$2-P12+12,12)</f>
+      <c r="Z13" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>2</v>
       </c>
-      <c r="AA13" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z13+$AA$2,1)</f>
+      <c r="AA13" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>46204</v>
       </c>
       <c r="AC13" s="10" t="s">
@@ -6809,18 +6762,18 @@
       </c>
       <c r="AD13" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE13" s="10" t="str">
         <f>_xll.BDP(AC13, "MATURITY")</f>
-        <v>7/20/2036</v>
+        <v>7/23/2036</v>
       </c>
       <c r="AF13" s="10">
         <f>_xll.BDP(AC13, "PX_LAST")</f>
-        <v>2.3925000000000001</v>
+        <v>2.4169999999999998</v>
       </c>
       <c r="AG13" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="AI13" s="14">
@@ -6831,7 +6784,7 @@
       </c>
       <c r="AK13" s="14">
         <f>_xll.BDP(AJ13, "PX_LAST")</f>
-        <v>1</v>
+        <v>0.99980000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.25">
@@ -6842,13 +6795,13 @@
         <v>3</v>
       </c>
       <c r="G14" s="20">
-        <v>46203</v>
+        <v>46213</v>
       </c>
       <c r="H14">
-        <v>332.92642999999998</v>
+        <v>333.63055000000003</v>
       </c>
       <c r="I14" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J14" s="26"/>
@@ -6877,7 +6830,7 @@
         <f>DATEVALUE(_xll.BDP(Q14, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>46235</v>
       </c>
-      <c r="U14" s="36" cm="1">
+      <c r="U14" s="12" cm="1">
         <f t="array" ref="U14">_xll.qwCalAddMonths("All",V14,-3)</f>
         <v>46508</v>
       </c>
@@ -6887,18 +6840,18 @@
       </c>
       <c r="W14" s="9">
         <f>_xll.BDP(Q14, "PX_MID")</f>
-        <v>341.22640000000001</v>
+        <v>341.64</v>
       </c>
       <c r="X14" t="b">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Z14" s="40">
-        <f ca="1">MOD($Z$2-P13+12,12)</f>
+      <c r="Z14" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-      <c r="AA14" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z14+$AA$2,1)</f>
+      <c r="AA14" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>46235</v>
       </c>
       <c r="AC14" s="10" t="s">
@@ -6906,15 +6859,15 @@
       </c>
       <c r="AD14" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE14" s="10" t="str">
         <f>_xll.BDP(AC14, "MATURITY")</f>
-        <v>7/20/2041</v>
+        <v>7/23/2041</v>
       </c>
       <c r="AF14" s="10">
         <f>_xll.BDP(AC14, "PX_LAST")</f>
-        <v>2.3849999999999998</v>
+        <v>2.3978999999999999</v>
       </c>
       <c r="AG14" s="10">
         <v>15</v>
@@ -6927,18 +6880,18 @@
       </c>
       <c r="AK14" s="14">
         <f>_xll.BDP(AJ14, "PX_LAST")</f>
-        <v>0.997</v>
+        <v>0.99709999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="G15" s="20">
-        <v>46202</v>
+        <v>46212</v>
       </c>
       <c r="H15">
-        <v>332.83287000000001</v>
+        <v>333.56270999999998</v>
       </c>
       <c r="I15" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J15" s="26"/>
@@ -6967,7 +6920,7 @@
         <f>DATEVALUE(_xll.BDP(Q15, "SWAP_EFFECTIVE_DATE_RT"))</f>
         <v>46266</v>
       </c>
-      <c r="U15" s="36" cm="1">
+      <c r="U15" s="12" cm="1">
         <f t="array" ref="U15">_xll.qwCalAddMonths("All",V15,-3)</f>
         <v>46539</v>
       </c>
@@ -6977,18 +6930,18 @@
       </c>
       <c r="W15" s="35">
         <f>_xll.BDP(Q15, "PX_MID")</f>
-        <v>341.81659999999999</v>
+        <v>342.40989999999999</v>
       </c>
       <c r="X15" t="b">
         <f>V15&gt;V14</f>
         <v>1</v>
       </c>
-      <c r="Z15" s="40">
-        <f ca="1">MOD($Z$2-P14+12,12)</f>
+      <c r="Z15" s="39">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="41">
-        <f ca="1">DATE(YEAR(strippingDate),MONTH(DATE(YEAR(strippingDate),MONTH(strippingDate),1))-Z15+$AA$2,1)</f>
+      <c r="AA15" s="40">
+        <f t="shared" ca="1" si="0"/>
         <v>46266</v>
       </c>
       <c r="AC15" s="10" t="s">
@@ -6996,15 +6949,15 @@
       </c>
       <c r="AD15" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE15" s="10" t="str">
         <f>_xll.BDP(AC15, "MATURITY")</f>
-        <v>7/20/2046</v>
+        <v>7/23/2046</v>
       </c>
       <c r="AF15" s="10">
         <f>_xll.BDP(AC15, "PX_LAST")</f>
-        <v>2.3620000000000001</v>
+        <v>2.3693</v>
       </c>
       <c r="AG15" s="10">
         <v>20</v>
@@ -7017,7 +6970,7 @@
       </c>
       <c r="AK15" s="14">
         <f>_xll.BDP(AJ15, "PX_LAST")</f>
-        <v>0.995</v>
+        <v>0.99450000000000005</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.25">
@@ -7025,13 +6978,13 @@
       <c r="B16" s="2"/>
       <c r="D16" s="3"/>
       <c r="G16" s="20">
-        <v>46199</v>
+        <v>46211</v>
       </c>
       <c r="H16">
-        <v>332.55216999999999</v>
+        <v>333.49486999999999</v>
       </c>
       <c r="I16" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J16" s="26"/>
@@ -7048,15 +7001,15 @@
       </c>
       <c r="AD16" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE16" s="10" t="str">
         <f>_xll.BDP(AC16, "MATURITY")</f>
-        <v>7/20/2051</v>
+        <v>7/23/2051</v>
       </c>
       <c r="AF16" s="10">
         <f>_xll.BDP(AC16, "PX_LAST")</f>
-        <v>2.3330000000000002</v>
+        <v>2.3348</v>
       </c>
       <c r="AG16" s="10">
         <v>25</v>
@@ -7066,13 +7019,13 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="G17" s="20">
-        <v>46198</v>
+        <v>46210</v>
       </c>
       <c r="H17">
-        <v>332.45859999999999</v>
+        <v>333.42703</v>
       </c>
       <c r="I17" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f ca="1">IF((G17=$C$20),$D$20,0)</f>
         <v>0</v>
       </c>
       <c r="J17" s="26"/>
@@ -7090,15 +7043,15 @@
       </c>
       <c r="AD17" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>46221</v>
+        <v>46226</v>
       </c>
       <c r="AE17" s="10" t="str">
         <f>_xll.BDP(AC17, "MATURITY")</f>
-        <v>7/20/2056</v>
+        <v>7/23/2056</v>
       </c>
       <c r="AF17" s="10">
         <f>_xll.BDP(AC17, "PX_LAST")</f>
-        <v>2.3340000000000001</v>
+        <v>2.3365</v>
       </c>
       <c r="AG17" s="10">
         <v>30</v>
@@ -7107,13 +7060,13 @@
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="E18" s="26"/>
       <c r="G18" s="20">
-        <v>46197</v>
+        <v>46209</v>
       </c>
       <c r="H18">
-        <v>332.36502999999999</v>
+        <v>333.35919000000001</v>
       </c>
       <c r="I18" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J18" s="26"/>
@@ -7135,13 +7088,13 @@
         <v>575</v>
       </c>
       <c r="G19" s="20">
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="H19">
-        <v>332.27147000000002</v>
+        <v>333.08784000000003</v>
       </c>
       <c r="I19" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J19" s="26"/>
@@ -7156,8 +7109,8 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <f t="shared" ref="A20:A22" ca="1" si="5">C20-$D$10</f>
-        <v>4</v>
+        <f t="shared" ref="A20:A22" ca="1" si="6">C20-$D$10</f>
+        <v>2</v>
       </c>
       <c r="B20" s="34">
         <f ca="1">DATE(YEAR(C20), MONTH(C20)-3,15)</f>
@@ -7165,20 +7118,20 @@
       </c>
       <c r="C20" s="23">
         <f ca="1">D11</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="D20" s="19" cm="1">
         <f t="array" aca="1" ref="D20" ca="1">INDEX(_xlfn.ANCHORARRAY(K3),MATCH(LaggedEOM,K3:K13,0),2)+(DAY(spotDate)-1)/DAY(EOMONTH(spotDate,0))*(INDEX(_xlfn.ANCHORARRAY(K3),MATCH(LaggedEOM,K3:K13,0)-1,2)-INDEX(_xlfn.ANCHORARRAY(K3),MATCH(LaggedEOM,K3:K13,0),2))</f>
-        <v>334.30893548387098</v>
+        <v>334.51245161290319</v>
       </c>
       <c r="G20" s="20">
-        <v>46195</v>
+        <v>46204</v>
       </c>
       <c r="H20">
-        <v>332.17790000000002</v>
+        <v>333.02</v>
       </c>
       <c r="I20" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J20" s="26"/>
@@ -7194,22 +7147,22 @@
         <v>0</v>
       </c>
       <c r="O20" s="2">
-        <f t="shared" ref="O20:O51" ca="1" si="6">N20+$D$10</f>
-        <v>46219</v>
+        <f t="shared" ref="O20:O51" ca="1" si="7">N20+$D$10</f>
+        <v>46224</v>
       </c>
       <c r="P20" cm="1">
         <f t="array" aca="1" ref="P20" ca="1">_xll.qwDataInterp(N20,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>334.32696482545293</v>
+        <v>334.52319023041468</v>
       </c>
       <c r="Q20" s="3">
-        <f t="shared" ref="Q20:Q51" ca="1" si="7">VLOOKUP(MONTH(O20),$AI$4:$AK$15,3,0)*P20</f>
-        <v>334.99561875510386</v>
+        <f t="shared" ref="Q20:Q51" ca="1" si="8">VLOOKUP(MONTH(O20),$AI$4:$AK$15,3,0)*P20</f>
+        <v>335.22568892989852</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <f t="shared" ca="1" si="5"/>
-        <v>77</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>72</v>
       </c>
       <c r="B21" s="33">
         <f>DATE(YEAR(V15), MONTH(V15)-3,15)</f>
@@ -7221,17 +7174,17 @@
       </c>
       <c r="D21" s="35">
         <f>W4</f>
-        <v>333.97989999999999</v>
+        <v>334.13659999999999</v>
       </c>
       <c r="E21" s="4"/>
       <c r="G21" s="20">
-        <v>46191</v>
+        <v>46203</v>
       </c>
       <c r="H21">
-        <v>331.80363</v>
+        <v>332.92642999999998</v>
       </c>
       <c r="I21" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J21" s="26"/>
@@ -7249,48 +7202,48 @@
         <v>100</v>
       </c>
       <c r="O21" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>46319</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>46324</v>
       </c>
       <c r="P21" cm="1">
         <f t="array" aca="1" ref="P21" ca="1">_xll.qwDataInterp(N21,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>334.81836129032257</v>
+        <v>335.37695483870965</v>
       </c>
       <c r="Q21" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>334.81836129032257</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>335.30987944774193</v>
       </c>
       <c r="R21">
         <f ca="1">EXP(LN(P21/$P$20)*1/((O21-$O$20)/365))-1</f>
-        <v>5.3752557610911023E-3</v>
+        <v>9.347016065999858E-3</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
-        <f t="shared" ca="1" si="5"/>
-        <v>108</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>103</v>
       </c>
       <c r="B22" s="33">
-        <f t="shared" ref="B22:B32" si="8">DATE(YEAR(V4), MONTH(V4)-3,15)</f>
+        <f t="shared" ref="B22:B32" si="9">DATE(YEAR(V4), MONTH(V4)-3,15)</f>
         <v>46218</v>
       </c>
       <c r="C22" s="24">
-        <f t="shared" ref="C22:C31" si="9">DATE(YEAR(V5), MONTH(V5),DAY(V5))</f>
+        <f t="shared" ref="C22:C31" si="10">DATE(YEAR(V5), MONTH(V5),DAY(V5))</f>
         <v>46327</v>
       </c>
       <c r="D22" s="35">
         <f>W5</f>
-        <v>335.11</v>
+        <v>335.50984999999997</v>
       </c>
       <c r="E22" s="4"/>
       <c r="G22" s="20">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="H22">
-        <v>331.71006999999997</v>
+        <v>332.83287000000001</v>
       </c>
       <c r="I22" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J22" s="26"/>
@@ -7309,19 +7262,19 @@
       </c>
       <c r="O22" s="2">
         <f ca="1">N22+$D$10</f>
-        <v>46419</v>
+        <v>46424</v>
       </c>
       <c r="P22" cm="1">
         <f t="array" aca="1" ref="P22" ca="1">_xll.qwDataInterp(N22,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>335.08994999999999</v>
+        <v>335.5027482142857</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>334.41977009999999</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>334.89884326749996</v>
       </c>
       <c r="R22">
         <f ca="1">EXP(LN(P22/$P$20)*1/((O22-$O$20)/365))-1</f>
-        <v>4.1688489100415449E-3</v>
+        <v>5.3504580358290088E-3</v>
       </c>
       <c r="AA22" t="s">
         <v>490</v>
@@ -7338,30 +7291,30 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
-        <f t="shared" ref="A23:A44" ca="1" si="10">C23-$D$10</f>
-        <v>138</v>
+        <f t="shared" ref="A23:A44" ca="1" si="11">C23-$D$10</f>
+        <v>133</v>
       </c>
       <c r="B23" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46249</v>
       </c>
       <c r="C23" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46357</v>
       </c>
       <c r="D23" s="35">
         <f>W6</f>
-        <v>335.64</v>
+        <v>336.1</v>
       </c>
       <c r="E23" s="4"/>
       <c r="G23" s="20">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="H23">
-        <v>331.61649999999997</v>
+        <v>332.55216999999999</v>
       </c>
       <c r="I23" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J23" s="26"/>
@@ -7379,20 +7332,20 @@
         <v>300</v>
       </c>
       <c r="O23" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>46519</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>46524</v>
       </c>
       <c r="P23" cm="1">
         <f t="array" aca="1" ref="P23" ca="1">_xll.qwDataInterp(N23,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>338.17563225806452</v>
+        <v>338.87861129032257</v>
       </c>
       <c r="Q23" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>339.19015915483868</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>339.89524712419347</v>
       </c>
       <c r="R23">
-        <f t="shared" ref="R23:R52" ca="1" si="11">EXP(LN(P23/$P$20)*1/((O23-$O$20)/365))-1</f>
-        <v>1.4023300559075524E-2</v>
+        <f t="shared" ref="R23:R52" ca="1" si="12">EXP(LN(P23/$P$20)*1/((O23-$O$20)/365))-1</f>
+        <v>1.5863009703026787E-2</v>
       </c>
       <c r="AA23" s="2">
         <f ca="1">K3</f>
@@ -7413,30 +7366,30 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
-        <f t="shared" ca="1" si="10"/>
-        <v>169</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>164</v>
       </c>
       <c r="B24" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46280</v>
       </c>
       <c r="C24" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46388</v>
       </c>
       <c r="D24" s="35">
-        <f t="shared" ref="D24:D31" si="12">W7</f>
-        <v>335.51004999999998</v>
+        <f t="shared" ref="D24:D31" si="13">W7</f>
+        <v>335.96985000000001</v>
       </c>
       <c r="E24" s="4"/>
       <c r="G24" s="20">
-        <v>46188</v>
+        <v>46198</v>
       </c>
       <c r="H24">
-        <v>331.52292999999997</v>
+        <v>332.45859999999999</v>
       </c>
       <c r="I24" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J24" s="26"/>
@@ -7450,31 +7403,31 @@
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="3">
-        <f t="shared" ref="N24:N85" si="13">N23+100</f>
+        <f t="shared" ref="N24:N85" si="14">N23+100</f>
         <v>400</v>
       </c>
       <c r="O24" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>46619</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>46624</v>
       </c>
       <c r="P24" cm="1">
         <f t="array" aca="1" ref="P24" ca="1">_xll.qwDataInterp(N24,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>341.58813548387099</v>
+        <v>342.23605161290322</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>342.27131175483873</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>342.85207650580645</v>
       </c>
       <c r="R24">
         <f ca="1">EXP(LN(P24/$P$20)*1/((O24-$O$20)/365))-1</f>
-        <v>1.9799693437420718E-2</v>
+        <v>2.1017811453843738E-2</v>
       </c>
       <c r="AA24" s="2">
         <f ca="1">K4</f>
         <v>46173</v>
       </c>
       <c r="AB24" s="2">
-        <f t="shared" ref="AB24:AB27" ca="1" si="14">DATE(YEAR(AA24),MONTH(AA24),1)</f>
+        <f t="shared" ref="AB24:AB27" ca="1" si="15">DATE(YEAR(AA24),MONTH(AA24),1)</f>
         <v>46143</v>
       </c>
       <c r="AC24" s="2">
@@ -7486,36 +7439,36 @@
         <v>335.12299999999999</v>
       </c>
       <c r="AE24">
-        <f t="shared" ref="AE24" ca="1" si="15">AC23-AC24</f>
+        <f t="shared" ref="AE24" ca="1" si="16">AC23-AC24</f>
         <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
-        <f t="shared" ca="1" si="10"/>
-        <v>200</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>195</v>
       </c>
       <c r="B25" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46310</v>
       </c>
       <c r="C25" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46419</v>
       </c>
       <c r="D25" s="35">
         <f>W8</f>
-        <v>335.08994999999999</v>
+        <v>335.50990000000002</v>
       </c>
       <c r="E25" s="4"/>
       <c r="G25" s="20">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="H25">
-        <v>331.24223000000001</v>
+        <v>332.36502999999999</v>
       </c>
       <c r="I25" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J25" s="26"/>
@@ -7529,31 +7482,31 @@
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>500</v>
       </c>
       <c r="O25" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>46719</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>46724</v>
       </c>
       <c r="P25" cm="1">
         <f t="array" aca="1" ref="P25" ca="1">_xll.qwDataInterp(N25,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>343.94852465151814</v>
+        <v>344.63814087323374</v>
       </c>
       <c r="Q25" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>342.91667907756357</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>342.74263109843099</v>
       </c>
       <c r="R25">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.0927948543443708E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.1983983432336762E-2</v>
       </c>
       <c r="AA25" s="2">
         <f ca="1">K5</f>
         <v>46142</v>
       </c>
       <c r="AB25" s="2">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="15"/>
         <v>46113</v>
       </c>
       <c r="AC25" s="2">
@@ -7575,30 +7528,30 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
-        <f t="shared" ca="1" si="10"/>
-        <v>228</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>223</v>
       </c>
       <c r="B26" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46341</v>
       </c>
       <c r="C26" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46447</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" si="12"/>
-        <v>335.06995000000001</v>
+        <f t="shared" si="13"/>
+        <v>335.46985000000001</v>
       </c>
       <c r="E26" s="4"/>
       <c r="G26" s="20">
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="H26">
-        <v>331.14866999999998</v>
+        <v>332.27147000000002</v>
       </c>
       <c r="I26" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J26" s="26"/>
@@ -7612,31 +7565,31 @@
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>600</v>
       </c>
       <c r="O26" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>46819</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>46824</v>
       </c>
       <c r="P26" cm="1">
         <f t="array" aca="1" ref="P26" ca="1">_xll.qwDataInterp(N26,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>346.37116630097051</v>
+        <v>347.03409880144204</v>
       </c>
       <c r="Q26" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>346.71753746727143</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>347.24231926072287</v>
       </c>
       <c r="R26">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.1763258488800119E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.2587393864522687E-2</v>
       </c>
       <c r="AA26" s="2">
         <f ca="1">K6</f>
         <v>46112</v>
       </c>
       <c r="AB26" s="2">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="15"/>
         <v>46082</v>
       </c>
       <c r="AC26" s="2">
@@ -7648,36 +7601,36 @@
         <v>330.21300000000002</v>
       </c>
       <c r="AE26">
-        <f t="shared" ref="AE26:AE27" ca="1" si="16">AC25-AC26</f>
+        <f t="shared" ref="AE26:AE27" ca="1" si="17">AC25-AC26</f>
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
-        <f t="shared" ca="1" si="10"/>
-        <v>259</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>254</v>
       </c>
       <c r="B27" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46371</v>
       </c>
       <c r="C27" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46478</v>
       </c>
       <c r="D27" s="35">
-        <f t="shared" si="12"/>
-        <v>336.42005</v>
+        <f t="shared" si="13"/>
+        <v>336.84994999999998</v>
       </c>
       <c r="E27" s="4"/>
       <c r="G27" s="20">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="H27">
-        <v>331.05509999999998</v>
+        <v>332.17790000000002</v>
       </c>
       <c r="I27" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J27" s="26"/>
@@ -7685,31 +7638,31 @@
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>700</v>
       </c>
       <c r="O27" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>46919</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>46924</v>
       </c>
       <c r="P27" cm="1">
         <f t="array" aca="1" ref="P27" ca="1">_xll.qwDataInterp(N27,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>348.79380795042294</v>
+        <v>349.43005672965035</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>349.84018937427419</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>350.44340389416629</v>
       </c>
       <c r="R27">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.2334247377854055E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.299319229659158E-2</v>
       </c>
       <c r="AA27" s="2">
         <f ca="1">K7</f>
         <v>46081</v>
       </c>
       <c r="AB27" s="2">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="15"/>
         <v>46054</v>
       </c>
       <c r="AC27" s="2">
@@ -7721,36 +7674,36 @@
         <v>326.78500000000003</v>
       </c>
       <c r="AE27">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ca="1" si="17"/>
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
-        <f t="shared" ca="1" si="10"/>
-        <v>289</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>284</v>
       </c>
       <c r="B28" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46402</v>
       </c>
       <c r="C28" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46508</v>
       </c>
       <c r="D28" s="35">
-        <f t="shared" si="12"/>
-        <v>337.69</v>
+        <f t="shared" si="13"/>
+        <v>338.11984999999999</v>
       </c>
       <c r="E28" s="4"/>
       <c r="G28" s="20">
-        <v>46182</v>
+        <v>46191</v>
       </c>
       <c r="H28">
-        <v>330.96152999999998</v>
+        <v>331.80363</v>
       </c>
       <c r="I28" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J28" s="26"/>
@@ -7758,33 +7711,33 @@
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>800</v>
       </c>
       <c r="O28" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47019</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47024</v>
       </c>
       <c r="P28" cm="1">
         <f t="array" aca="1" ref="P28" ca="1">_xll.qwDataInterp(N28,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>351.22035705534313</v>
+        <v>351.85545368505996</v>
       </c>
       <c r="Q28" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>351.92279776945384</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>352.38323686558755</v>
       </c>
       <c r="R28">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.2745377323947213E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.3314760502477494E-2</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
-        <f t="shared" ca="1" si="10"/>
-        <v>320</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>315</v>
       </c>
       <c r="B29" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46433</v>
       </c>
       <c r="C29" s="24">
@@ -7793,17 +7746,17 @@
       </c>
       <c r="D29" s="35">
         <f>W12</f>
-        <v>339.05860000000001</v>
+        <v>339.58994999999999</v>
       </c>
       <c r="E29" s="4"/>
       <c r="G29" s="20">
-        <v>46181</v>
+        <v>46190</v>
       </c>
       <c r="H29">
-        <v>330.86797000000001</v>
+        <v>331.71006999999997</v>
       </c>
       <c r="I29" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J29" s="26"/>
@@ -7811,67 +7764,67 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>900</v>
       </c>
       <c r="O29" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47119</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47124</v>
       </c>
       <c r="P29" cm="1">
         <f t="array" aca="1" ref="P29" ca="1">_xll.qwDataInterp(N29,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>353.64901017474602</v>
+        <v>354.29535045983738</v>
       </c>
       <c r="Q29" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>352.23441413404703</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>352.94902812808999</v>
       </c>
       <c r="R29">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.304792263276112E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.3562203323119091E-2</v>
       </c>
       <c r="AD29" t="s">
         <v>494</v>
       </c>
       <c r="AE29" s="15">
         <f>AF8</f>
-        <v>2.4020000000000001</v>
+        <v>2.4329000000000001</v>
       </c>
       <c r="AF29">
         <f>(1+AE29/100)^AG8</f>
-        <v>1.1260098623004526</v>
+        <v>1.1277097660726749</v>
       </c>
       <c r="AG29">
         <f ca="1">AF25*AF29</f>
-        <v>376.8934807468595</v>
+        <v>377.46246568304701</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
-        <f t="shared" ca="1" si="10"/>
-        <v>350</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>345</v>
       </c>
       <c r="B30" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46461</v>
       </c>
       <c r="C30" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46569</v>
       </c>
       <c r="D30" s="35">
         <f>W13</f>
-        <v>340.18405000000001</v>
+        <v>340.64</v>
       </c>
       <c r="E30" s="4"/>
       <c r="G30" s="20">
-        <v>46178</v>
+        <v>46189</v>
       </c>
       <c r="H30">
-        <v>330.58726999999999</v>
+        <v>331.61649999999997</v>
       </c>
       <c r="I30" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J30" s="26"/>
@@ -7879,24 +7832,24 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="O30" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47219</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47224</v>
       </c>
       <c r="P30" cm="1">
         <f t="array" aca="1" ref="P30" ca="1">_xll.qwDataInterp(N30,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>356.07766329414892</v>
+        <v>356.73524723461486</v>
       </c>
       <c r="Q30" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>357.14589628403132</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>357.55573830325449</v>
       </c>
       <c r="R30">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3272408254412014E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.3742478784605003E-2</v>
       </c>
       <c r="AD30" t="s">
         <v>493</v>
@@ -7915,30 +7868,30 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
-        <f t="shared" ca="1" si="10"/>
-        <v>381</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>376</v>
       </c>
       <c r="B31" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46492</v>
       </c>
       <c r="C31" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>46600</v>
       </c>
       <c r="D31" s="35">
-        <f t="shared" si="12"/>
-        <v>341.22640000000001</v>
+        <f t="shared" si="13"/>
+        <v>341.64</v>
       </c>
       <c r="E31" s="4"/>
       <c r="G31" s="20">
-        <v>46177</v>
+        <v>46188</v>
       </c>
       <c r="H31">
-        <v>330.49369999999999</v>
+        <v>331.52292999999997</v>
       </c>
       <c r="I31" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J31" s="26"/>
@@ -7946,33 +7899,33 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1100</v>
       </c>
       <c r="O31" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47319</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47324</v>
       </c>
       <c r="P31" cm="1">
         <f t="array" aca="1" ref="P31" ca="1">_xll.qwDataInterp(N31,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>358.50631641355182</v>
+        <v>359.17544970300401</v>
       </c>
       <c r="Q31" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>359.22332904637892</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>359.9297181473803</v>
       </c>
       <c r="R31">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3440316380464621E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.3874396466057712E-2</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
-        <f t="shared" ca="1" si="10"/>
-        <v>412</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>407</v>
       </c>
       <c r="B32" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46522</v>
       </c>
       <c r="C32" s="24">
@@ -7981,17 +7934,17 @@
       </c>
       <c r="D32" s="35">
         <f>W15</f>
-        <v>341.81659999999999</v>
+        <v>342.40989999999999</v>
       </c>
       <c r="E32" s="4"/>
       <c r="G32" s="20">
-        <v>46176</v>
+        <v>46185</v>
       </c>
       <c r="H32">
-        <v>330.40012999999999</v>
+        <v>331.24223000000001</v>
       </c>
       <c r="I32" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J32" s="26"/>
@@ -7999,52 +7952,52 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1200</v>
       </c>
       <c r="O32" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47419</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47424</v>
       </c>
       <c r="P32" cm="1">
         <f t="array" aca="1" ref="P32" ca="1">_xll.qwDataInterp(N32,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>360.94805006134737</v>
+        <v>361.63063115836837</v>
       </c>
       <c r="Q32" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>360.94805006134737</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>360.58190232800911</v>
       </c>
       <c r="R32">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.357725549259837E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.398286557724516E-2</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>735</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>733</v>
       </c>
       <c r="B33" s="25">
         <f>DATE(YEAR(AE5), MONTH(AE5)-3,DAY(AE5))</f>
-        <v>46863</v>
+        <v>46866</v>
       </c>
       <c r="C33" s="25">
-        <f t="shared" ref="C33:C44" si="17">DATE(YEAR(AE5), MONTH(AE5),DAY(AE5))</f>
-        <v>46954</v>
-      </c>
-      <c r="D33" s="37">
+        <f t="shared" ref="C33:C44" si="18">DATE(YEAR(AE5), MONTH(AE5),DAY(AE5))</f>
+        <v>46957</v>
+      </c>
+      <c r="D33" s="36">
         <f ca="1">$D$20*(1+AF5/100)^AG5</f>
-        <v>349.64173252773128</v>
+        <v>350.22072284595907</v>
       </c>
       <c r="E33" s="4"/>
-      <c r="G33" s="21">
-        <v>46175</v>
-      </c>
-      <c r="H33" s="22">
-        <v>330.30657000000002</v>
+      <c r="G33" s="20">
+        <v>46184</v>
+      </c>
+      <c r="H33">
+        <v>331.14866999999998</v>
       </c>
       <c r="I33" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J33" s="26"/>
@@ -8052,52 +8005,52 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1300</v>
       </c>
       <c r="O33" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47519</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47524</v>
       </c>
       <c r="P33" cm="1">
         <f t="array" aca="1" ref="P33" ca="1">_xll.qwDataInterp(N33,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>363.38978370914293</v>
+        <v>364.08581261373274</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>362.66300414172463</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>363.43045815102801</v>
       </c>
       <c r="R33">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3679988093457727E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4061402775475305E-2</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>1100</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>1098</v>
       </c>
       <c r="B34" s="25">
-        <f t="shared" ref="B34:B44" si="18">DATE(YEAR(AE6), MONTH(AE6)-3,DAY(AE6))</f>
-        <v>47228</v>
+        <f t="shared" ref="B34:B44" si="19">DATE(YEAR(AE6), MONTH(AE6)-3,DAY(AE6))</f>
+        <v>47231</v>
       </c>
       <c r="C34" s="25">
-        <f t="shared" si="17"/>
-        <v>47319</v>
-      </c>
-      <c r="D34" s="37">
-        <f t="shared" ref="D34:D44" ca="1" si="19">$D$20*(1+AF6/100)^AG6</f>
-        <v>358.50631641355182</v>
+        <f t="shared" si="18"/>
+        <v>47322</v>
+      </c>
+      <c r="D34" s="36">
+        <f t="shared" ref="D34:D44" ca="1" si="20">$D$20*(1+AF6/100)^AG6</f>
+        <v>359.12634607389674</v>
       </c>
       <c r="E34" s="4"/>
-      <c r="G34" s="21">
-        <v>46174</v>
-      </c>
-      <c r="H34" s="29">
-        <v>330.21300000000002</v>
+      <c r="G34" s="20">
+        <v>46183</v>
+      </c>
+      <c r="H34">
+        <v>331.05509999999998</v>
       </c>
       <c r="I34" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J34" s="26"/>
@@ -8105,52 +8058,52 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1400</v>
       </c>
       <c r="O34" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47619</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47624</v>
       </c>
       <c r="P34" cm="1">
         <f t="array" aca="1" ref="P34" ca="1">_xll.qwDataInterp(N34,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>365.83151735693849</v>
+        <v>366.54099406909711</v>
       </c>
       <c r="Q34" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>366.92901190900926</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>367.64061705130439</v>
       </c>
       <c r="R34">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3756001767544221E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4116583276562631E-2</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>1465</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>1463</v>
       </c>
       <c r="B35" s="25">
+        <f t="shared" si="19"/>
+        <v>47596</v>
+      </c>
+      <c r="C35" s="25">
         <f t="shared" si="18"/>
-        <v>47593</v>
-      </c>
-      <c r="C35" s="25">
-        <f t="shared" si="17"/>
-        <v>47684</v>
-      </c>
-      <c r="D35" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>367.41864422800563</v>
+        <v>47687</v>
+      </c>
+      <c r="D35" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>368.08775838597666</v>
       </c>
       <c r="E35" s="4"/>
       <c r="G35" s="20">
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="H35">
-        <v>329.88126</v>
+        <v>330.96152999999998</v>
       </c>
       <c r="I35" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J35" s="26"/>
@@ -8158,52 +8111,52 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="O35" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47719</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47724</v>
       </c>
       <c r="P35" cm="1">
         <f t="array" aca="1" ref="P35" ca="1">_xll.qwDataInterp(N35,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>368.28324147833428</v>
+        <v>369.01480607452424</v>
       </c>
       <c r="Q35" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>369.01980796129095</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>369.6790327254584</v>
       </c>
       <c r="R35">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3817544490837284E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4165809623944989E-2</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>1830</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>1828</v>
       </c>
       <c r="B36" s="25">
+        <f t="shared" si="19"/>
+        <v>47961</v>
+      </c>
+      <c r="C36" s="25">
         <f t="shared" si="18"/>
-        <v>47958</v>
-      </c>
-      <c r="C36" s="25">
-        <f t="shared" si="17"/>
-        <v>48049</v>
-      </c>
-      <c r="D36" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>376.43515841000448</v>
+        <v>48052</v>
+      </c>
+      <c r="D36" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>377.23295855678407</v>
       </c>
       <c r="E36" s="4"/>
       <c r="G36" s="20">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="H36">
-        <v>329.77068000000003</v>
+        <v>330.86797000000001</v>
       </c>
       <c r="I36" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J36" s="26"/>
@@ -8211,52 +8164,52 @@
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1600</v>
       </c>
       <c r="O36" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47819</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47824</v>
       </c>
       <c r="P36" cm="1">
         <f t="array" aca="1" ref="P36" ca="1">_xll.qwDataInterp(N36,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>370.75351933641616</v>
+        <v>371.52034036789615</v>
       </c>
       <c r="Q36" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>368.89975173973409</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>369.47697849587274</v>
       </c>
       <c r="R36">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3872734759779135E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4218334864596125E-2</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>2196</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2194</v>
       </c>
       <c r="B37" s="25">
+        <f t="shared" si="19"/>
+        <v>48327</v>
+      </c>
+      <c r="C37" s="25">
         <f t="shared" si="18"/>
-        <v>48324</v>
-      </c>
-      <c r="C37" s="25">
-        <f t="shared" si="17"/>
-        <v>48415</v>
-      </c>
-      <c r="D37" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>385.49971757593244</v>
+        <v>48418</v>
+      </c>
+      <c r="D37" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>386.40613243210549</v>
       </c>
       <c r="E37" s="4"/>
       <c r="G37" s="20">
-        <v>46169</v>
+        <v>46178</v>
       </c>
       <c r="H37">
-        <v>329.6601</v>
+        <v>330.58726999999999</v>
       </c>
       <c r="I37" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J37" s="26"/>
@@ -8264,52 +8217,52 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1700</v>
       </c>
       <c r="O37" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>47919</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>47924</v>
       </c>
       <c r="P37" cm="1">
         <f t="array" aca="1" ref="P37" ca="1">_xll.qwDataInterp(N37,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>373.22379719449805</v>
+        <v>374.02587466126806</v>
       </c>
       <c r="Q37" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>373.59702099169249</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>374.25029018606477</v>
       </c>
       <c r="R37">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3911674765301871E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4254680613017721E-2</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>2561</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2559</v>
       </c>
       <c r="B38" s="25">
+        <f t="shared" si="19"/>
+        <v>48692</v>
+      </c>
+      <c r="C38" s="25">
         <f t="shared" si="18"/>
-        <v>48689</v>
-      </c>
-      <c r="C38" s="25">
-        <f t="shared" si="17"/>
-        <v>48780</v>
-      </c>
-      <c r="D38" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>394.62567295066941</v>
+        <v>48783</v>
+      </c>
+      <c r="D38" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>395.61693422336128</v>
       </c>
       <c r="E38" s="4"/>
       <c r="G38" s="20">
-        <v>46168</v>
+        <v>46177</v>
       </c>
       <c r="H38">
-        <v>329.54951999999997</v>
+        <v>330.49369999999999</v>
       </c>
       <c r="I38" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J38" s="26"/>
@@ -8317,52 +8270,52 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1800</v>
       </c>
       <c r="O38" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48019</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48024</v>
       </c>
       <c r="P38" cm="1">
         <f t="array" aca="1" ref="P38" ca="1">_xll.qwDataInterp(N38,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>375.69407505257993</v>
+        <v>376.53140895463991</v>
       </c>
       <c r="Q38" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>376.82115727773765</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>377.62335004060833</v>
       </c>
       <c r="R38">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3937193187117956E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4277668356428528E-2</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>2926</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>2924</v>
       </c>
       <c r="B39" s="25">
+        <f t="shared" si="19"/>
+        <v>49057</v>
+      </c>
+      <c r="C39" s="25">
         <f t="shared" si="18"/>
-        <v>49054</v>
-      </c>
-      <c r="C39" s="25">
-        <f t="shared" si="17"/>
-        <v>49145</v>
-      </c>
-      <c r="D39" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>403.91795513419714</v>
+        <v>49148</v>
+      </c>
+      <c r="D39" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>405.0298843166637</v>
       </c>
       <c r="E39" s="4"/>
       <c r="G39" s="20">
-        <v>46164</v>
+        <v>46176</v>
       </c>
       <c r="H39">
-        <v>329.10719</v>
+        <v>330.40012999999999</v>
       </c>
       <c r="I39" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J39" s="26"/>
@@ -8370,52 +8323,52 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1900</v>
       </c>
       <c r="O39" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48119</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48124</v>
       </c>
       <c r="P39" cm="1">
         <f t="array" aca="1" ref="P39" ca="1">_xll.qwDataInterp(N39,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>378.16881726687592</v>
+        <v>379.0375173519293</v>
       </c>
       <c r="Q39" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>378.92515490140966</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>378.9617098484589</v>
       </c>
       <c r="R39">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3953843594760826E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4289821731264816E-2</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>3291</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>3289</v>
       </c>
       <c r="B40" s="25">
+        <f t="shared" si="19"/>
+        <v>49422</v>
+      </c>
+      <c r="C40" s="25">
         <f t="shared" si="18"/>
-        <v>49419</v>
-      </c>
-      <c r="C40" s="25">
-        <f t="shared" si="17"/>
-        <v>49510</v>
-      </c>
-      <c r="D40" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>413.48355049978176</v>
+        <v>49513</v>
+      </c>
+      <c r="D40" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>414.67448224284266</v>
       </c>
       <c r="E40" s="4"/>
-      <c r="G40" s="20">
-        <v>46163</v>
-      </c>
-      <c r="H40">
-        <v>328.99660999999998</v>
+      <c r="G40" s="21">
+        <v>46175</v>
+      </c>
+      <c r="H40" s="22">
+        <v>330.30657000000002</v>
       </c>
       <c r="I40" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J40" s="26"/>
@@ -8423,52 +8376,52 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="O40" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48219</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48224</v>
       </c>
       <c r="P40" cm="1">
         <f t="array" aca="1" ref="P40" ca="1">_xll.qwDataInterp(N40,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>380.64547277669232</v>
+        <v>381.54384901185313</v>
       </c>
       <c r="Q40" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>379.12289088558555</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>380.09398238560806</v>
       </c>
       <c r="R40">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3961765633969678E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4292697181691691E-2</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>3657</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>3655</v>
       </c>
       <c r="B41" s="25">
+        <f t="shared" si="19"/>
+        <v>49788</v>
+      </c>
+      <c r="C41" s="25">
         <f t="shared" si="18"/>
-        <v>49785</v>
-      </c>
-      <c r="C41" s="25">
-        <f t="shared" si="17"/>
-        <v>49876</v>
-      </c>
-      <c r="D41" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>423.47663419692583</v>
+        <v>49879</v>
+      </c>
+      <c r="D41" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>424.74941703470847</v>
       </c>
       <c r="E41" s="4"/>
-      <c r="G41" s="20">
-        <v>46162</v>
-      </c>
-      <c r="H41">
-        <v>328.88603000000001</v>
+      <c r="G41" s="21">
+        <v>46174</v>
+      </c>
+      <c r="H41" s="29">
+        <v>330.21300000000002</v>
       </c>
       <c r="I41" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J41" s="26"/>
@@ -8476,52 +8429,52 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2100</v>
       </c>
       <c r="O41" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48319</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48324</v>
       </c>
       <c r="P41" cm="1">
         <f t="array" aca="1" ref="P41" ca="1">_xll.qwDataInterp(N41,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>383.12212828650871</v>
+        <v>384.05018067177701</v>
       </c>
       <c r="Q41" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>384.2714946713682</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>384.93349608732211</v>
       </c>
       <c r="R41">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3961398687502689E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4287616426593939E-2</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>5483</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>5481</v>
       </c>
       <c r="B42" s="25">
+        <f t="shared" si="19"/>
+        <v>51614</v>
+      </c>
+      <c r="C42" s="25">
         <f t="shared" si="18"/>
-        <v>51611</v>
-      </c>
-      <c r="C42" s="25">
-        <f t="shared" si="17"/>
-        <v>51702</v>
-      </c>
-      <c r="D42" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>476.09432420413157</v>
+        <v>51705</v>
+      </c>
+      <c r="D42" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>477.28527949996936</v>
       </c>
       <c r="E42" s="4"/>
       <c r="G42" s="20">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="H42">
-        <v>328.75450000000001</v>
+        <v>329.88126</v>
       </c>
       <c r="I42" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J42" s="26"/>
@@ -8529,52 +8482,52 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2200</v>
       </c>
       <c r="O42" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48419</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48424</v>
       </c>
       <c r="P42" cm="1">
         <f t="array" aca="1" ref="P42" ca="1">_xll.qwDataInterp(N42,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>385.59972804579257</v>
+        <v>386.55754287250971</v>
       </c>
       <c r="Q42" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>386.37092750188418</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>387.36931371254195</v>
       </c>
       <c r="R42">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3954381768301447E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4276212948929565E-2</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>7309</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>7307</v>
       </c>
       <c r="B43" s="25">
+        <f t="shared" si="19"/>
+        <v>53440</v>
+      </c>
+      <c r="C43" s="25">
         <f t="shared" si="18"/>
-        <v>53437</v>
-      </c>
-      <c r="C43" s="25">
-        <f t="shared" si="17"/>
-        <v>53528</v>
-      </c>
-      <c r="D43" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>533.24063864107029</v>
+        <v>53531</v>
+      </c>
+      <c r="D43" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>534.32680332560187</v>
       </c>
       <c r="E43" s="4"/>
       <c r="G43" s="20">
-        <v>46160</v>
-      </c>
-      <c r="H43" s="27">
-        <v>328.66487000000001</v>
+        <v>46170</v>
+      </c>
+      <c r="H43">
+        <v>329.77068000000003</v>
       </c>
       <c r="I43" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J43" s="26"/>
@@ -8582,52 +8535,52 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2300</v>
       </c>
       <c r="O43" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48519</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48524</v>
       </c>
       <c r="P43" cm="1">
         <f t="array" aca="1" ref="P43" ca="1">_xll.qwDataInterp(N43,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>388.09998979229584</v>
+        <v>389.08105021257978</v>
       </c>
       <c r="Q43" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>386.93568982291896</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>387.95271516696329</v>
       </c>
       <c r="R43">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3950755095908827E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4265707288241956E-2</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
-        <f t="shared" ca="1" si="10"/>
-        <v>9135</v>
+        <f t="shared" ca="1" si="11"/>
+        <v>9133</v>
       </c>
       <c r="B44" s="25">
+        <f t="shared" si="19"/>
+        <v>55266</v>
+      </c>
+      <c r="C44" s="25">
         <f t="shared" si="18"/>
-        <v>55263</v>
-      </c>
-      <c r="C44" s="25">
-        <f t="shared" si="17"/>
-        <v>55354</v>
-      </c>
-      <c r="D44" s="37">
-        <f t="shared" ca="1" si="19"/>
-        <v>595.0324321790356</v>
+        <v>55357</v>
+      </c>
+      <c r="D44" s="36">
+        <f t="shared" ca="1" si="20"/>
+        <v>595.65654270262178</v>
       </c>
       <c r="E44" s="4"/>
       <c r="G44" s="20">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="H44">
-        <v>328.33312999999998</v>
+        <v>329.6601</v>
       </c>
       <c r="I44" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J44" s="26"/>
@@ -8635,36 +8588,36 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2400</v>
       </c>
       <c r="O44" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48619</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48624</v>
       </c>
       <c r="P44" cm="1">
         <f t="array" aca="1" ref="P44" ca="1">_xll.qwDataInterp(N44,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>390.60025153879911</v>
+        <v>391.60455755264985</v>
       </c>
       <c r="Q44" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>389.81905103572154</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>390.89966934905505</v>
       </c>
       <c r="R44">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3940967412554803E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4249524394082345E-2</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E45" s="4"/>
       <c r="G45" s="20">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="H45">
-        <v>328.22255000000001</v>
+        <v>329.54951999999997</v>
       </c>
       <c r="I45" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J45" s="26"/>
@@ -8672,36 +8625,36 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="O45" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48719</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48724</v>
       </c>
       <c r="P45" cm="1">
         <f t="array" aca="1" ref="P45" ca="1">_xll.qwDataInterp(N45,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>393.10051328530238</v>
+        <v>394.12806489271992</v>
       </c>
       <c r="Q45" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>394.27981482515827</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>395.31044908739801</v>
       </c>
       <c r="R45">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3925837383968362E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4228426613449594E-2</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E46" s="4"/>
       <c r="G46" s="20">
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="H46">
-        <v>328.11196999999999</v>
+        <v>329.10719</v>
       </c>
       <c r="I46" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J46" s="26"/>
@@ -8709,36 +8662,36 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2600</v>
       </c>
       <c r="O46" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48819</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48824</v>
       </c>
       <c r="P46" cm="1">
         <f t="array" aca="1" ref="P46" ca="1">_xll.qwDataInterp(N46,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>395.61854693740253</v>
+        <v>396.67427930233498</v>
       </c>
       <c r="Q46" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>396.40978403127735</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>397.26929072128848</v>
       </c>
       <c r="R46">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3912513610706343E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4211288471696513E-2</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E47" s="4"/>
       <c r="G47" s="20">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="H47">
-        <v>328.00139000000001</v>
+        <v>328.99660999999998</v>
       </c>
       <c r="I47" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J47" s="26"/>
@@ -8746,35 +8699,35 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2700</v>
       </c>
       <c r="O47" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>48919</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>48924</v>
       </c>
       <c r="P47" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">_xll.qwDataInterp(N47,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>398.16437767261561</v>
+        <v>399.25316973885617</v>
       </c>
       <c r="Q47" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>396.17355578425253</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>397.05727730529247</v>
       </c>
       <c r="R47">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3904233092381766E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4201047367280015E-2</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G48" s="20">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="H48">
-        <v>327.89080999999999</v>
+        <v>328.88603000000001</v>
       </c>
       <c r="I48" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J48" s="26"/>
@@ -8782,36 +8735,36 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2800</v>
       </c>
       <c r="O48" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>49019</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>49024</v>
       </c>
       <c r="P48" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">_xll.qwDataInterp(N48,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>400.71020840782865</v>
+        <v>401.83206017537742</v>
       </c>
       <c r="Q48" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>401.1109186162364</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>402.07315941148261</v>
       </c>
       <c r="R48">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3891087364454666E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4185967377987172E-2</v>
       </c>
     </row>
     <row r="49" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C49" s="2"/>
       <c r="G49" s="20">
-        <v>46150</v>
+        <v>46161</v>
       </c>
       <c r="H49">
-        <v>327.55905999999999</v>
+        <v>328.75450000000001</v>
       </c>
       <c r="I49" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J49" s="26"/>
@@ -8819,36 +8772,36 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2900</v>
       </c>
       <c r="O49" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>49119</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>49124</v>
       </c>
       <c r="P49" cm="1">
         <f t="array" aca="1" ref="P49" ca="1">_xll.qwDataInterp(N49,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>403.25603914304173</v>
+        <v>404.41095061189861</v>
       </c>
       <c r="Q49" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>404.4658072604708</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>405.58374236867309</v>
       </c>
       <c r="R49">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3873646641830559E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4166618105361914E-2</v>
       </c>
     </row>
     <row r="50" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C50" s="2"/>
       <c r="G50" s="20">
-        <v>46149</v>
-      </c>
-      <c r="H50">
-        <v>327.44848000000002</v>
+        <v>46160</v>
+      </c>
+      <c r="H50" s="27">
+        <v>328.66487000000001</v>
       </c>
       <c r="I50" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J50" s="26"/>
@@ -8856,36 +8809,36 @@
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
       <c r="N50" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3000</v>
       </c>
       <c r="O50" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>49219</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>49224</v>
       </c>
       <c r="P50" cm="1">
         <f t="array" aca="1" ref="P50" ca="1">_xll.qwDataInterp(N50,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>405.85728131790472</v>
+        <v>407.03807456978586</v>
       </c>
       <c r="Q50" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>405.85728131790472</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>406.95666695487193</v>
       </c>
       <c r="R50">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3869412529679224E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.415825840118746E-2</v>
       </c>
     </row>
     <row r="51" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C51" s="2"/>
       <c r="G51" s="20">
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="H51">
-        <v>327.33789999999999</v>
+        <v>328.33312999999998</v>
       </c>
       <c r="I51" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J51" s="26"/>
@@ -8893,36 +8846,36 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3100</v>
       </c>
       <c r="O51" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>49319</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>49324</v>
       </c>
       <c r="P51" cm="1">
         <f t="array" aca="1" ref="P51" ca="1">_xll.qwDataInterp(N51,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>408.47799237696898</v>
+        <v>409.68043016599933</v>
       </c>
       <c r="Q51" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>406.84408040746109</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>408.12364453136854</v>
       </c>
       <c r="R51">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3866245289101862E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.414989809438195E-2</v>
       </c>
     </row>
     <row r="52" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C52" s="2"/>
       <c r="G52" s="20">
-        <v>46147</v>
+        <v>46156</v>
       </c>
       <c r="H52">
-        <v>327.22732000000002</v>
+        <v>328.22255000000001</v>
       </c>
       <c r="I52" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J52" s="26"/>
@@ -8930,36 +8883,36 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3200</v>
       </c>
       <c r="O52" s="2">
-        <f t="shared" ref="O52:O83" ca="1" si="20">N52+$D$10</f>
-        <v>49419</v>
+        <f t="shared" ref="O52:O83" ca="1" si="21">N52+$D$10</f>
+        <v>49424</v>
       </c>
       <c r="P52" cm="1">
         <f t="array" aca="1" ref="P52" ca="1">_xll.qwDataInterp(N52,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>411.09870343603325</v>
+        <v>412.32278576221273</v>
       </c>
       <c r="Q52" s="3">
-        <f t="shared" ref="Q52:Q83" ca="1" si="21">VLOOKUP(MONTH(O52),$AI$4:$AK$15,3,0)*P52</f>
-        <v>412.33199954634131</v>
+        <f t="shared" ref="Q52:Q83" ca="1" si="22">VLOOKUP(MONTH(O52),$AI$4:$AK$15,3,0)*P52</f>
+        <v>413.27112816946578</v>
       </c>
       <c r="R52">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.3858468792947507E-2</v>
+        <f t="shared" ca="1" si="12"/>
+        <v>2.4137200739015263E-2</v>
       </c>
     </row>
     <row r="53" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C53" s="2"/>
-      <c r="G53" s="21">
-        <v>46146</v>
-      </c>
-      <c r="H53" s="22">
-        <v>327.11673999999999</v>
+      <c r="G53" s="20">
+        <v>46155</v>
+      </c>
+      <c r="H53">
+        <v>328.11196999999999</v>
       </c>
       <c r="I53" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J53" s="26"/>
@@ -8967,36 +8920,36 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3300</v>
       </c>
       <c r="O53" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>49519</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>49524</v>
       </c>
       <c r="P53" cm="1">
         <f t="array" aca="1" ref="P53" ca="1">_xll.qwDataInterp(N53,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>413.72928206610499</v>
+        <v>414.97728082948345</v>
       </c>
       <c r="Q53" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>414.55674063023719</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>415.72423993497654</v>
       </c>
       <c r="R53">
-        <f t="shared" ref="R53:R84" ca="1" si="22">EXP(LN(P53/$P$20)*1/((O53-$O$20)/365))-1</f>
-        <v>2.3849262340472244E-2</v>
+        <f t="shared" ref="R53:R84" ca="1" si="23">EXP(LN(P53/$P$20)*1/((O53-$O$20)/365))-1</f>
+        <v>2.4123934672108716E-2</v>
       </c>
     </row>
     <row r="54" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C54" s="2"/>
-      <c r="G54" s="21">
-        <v>46143</v>
-      </c>
-      <c r="H54" s="22">
-        <v>326.78500000000003</v>
+      <c r="G54" s="20">
+        <v>46154</v>
+      </c>
+      <c r="H54">
+        <v>328.00139000000001</v>
       </c>
       <c r="I54" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J54" s="26"/>
@@ -9004,36 +8957,36 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3400</v>
       </c>
       <c r="O54" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>49619</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>49624</v>
       </c>
       <c r="P54" cm="1">
         <f t="array" aca="1" ref="P54" ca="1">_xll.qwDataInterp(N54,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>416.45963280302959</v>
+        <v>417.72999525349047</v>
       </c>
       <c r="Q54" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>415.21025390462052</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>416.51857826725535</v>
       </c>
       <c r="R54">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3862489328840608E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4132803821347526E-2</v>
       </c>
     </row>
     <row r="55" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C55" s="2"/>
       <c r="G55" s="20">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="H55">
-        <v>326.73390000000001</v>
+        <v>327.89080999999999</v>
       </c>
       <c r="I55" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J55" s="26"/>
@@ -9041,36 +8994,36 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3500</v>
       </c>
       <c r="O55" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>49719</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>49724</v>
       </c>
       <c r="P55" cm="1">
         <f t="array" aca="1" ref="P55" ca="1">_xll.qwDataInterp(N55,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>419.1899835399542</v>
+        <v>420.48270967749755</v>
       </c>
       <c r="Q55" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>418.3516035728743</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>419.72584080007806</v>
       </c>
       <c r="R55">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3870371084691699E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4136528303529747E-2</v>
       </c>
     </row>
     <row r="56" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C56" s="2"/>
       <c r="G56" s="20">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="H56">
-        <v>326.68279999999999</v>
+        <v>327.55905999999999</v>
       </c>
       <c r="I56" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J56" s="26"/>
@@ -9078,36 +9031,36 @@
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3600</v>
       </c>
       <c r="O56" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>49819</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>49824</v>
       </c>
       <c r="P56" cm="1">
         <f t="array" aca="1" ref="P56" ca="1">_xll.qwDataInterp(N56,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>421.9203342768788</v>
+        <v>423.23542410150458</v>
       </c>
       <c r="Q56" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>423.18609527970938</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>424.50513037380904</v>
       </c>
       <c r="R56">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3873410873378242E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4135595635560447E-2</v>
       </c>
     </row>
     <row r="57" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C57" s="2"/>
       <c r="G57" s="20">
-        <v>46140</v>
+        <v>46149</v>
       </c>
       <c r="H57">
-        <v>326.63170000000002</v>
+        <v>327.44848000000002</v>
       </c>
       <c r="I57" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J57" s="26"/>
@@ -9115,36 +9068,36 @@
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3700</v>
       </c>
       <c r="O57" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>49919</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>49924</v>
       </c>
       <c r="P57" cm="1">
         <f t="array" aca="1" ref="P57" ca="1">_xll.qwDataInterp(N57,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>424.71571452020612</v>
+        <v>426.04411244047884</v>
       </c>
       <c r="Q57" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>425.56514594924653</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>426.68317860913959</v>
       </c>
       <c r="R57">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3887522795165594E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4143713792723398E-2</v>
       </c>
     </row>
     <row r="58" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C58" s="2"/>
       <c r="G58" s="20">
-        <v>46139</v>
+        <v>46148</v>
       </c>
       <c r="H58">
-        <v>326.5806</v>
+        <v>327.33789999999999</v>
       </c>
       <c r="I58" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J58" s="26"/>
@@ -9152,36 +9105,36 @@
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3800</v>
       </c>
       <c r="O58" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50019</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50024</v>
       </c>
       <c r="P58" cm="1">
         <f t="array" aca="1" ref="P58" ca="1">_xll.qwDataInterp(N58,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>427.59729666736968</v>
+        <v>428.92121334219087</v>
       </c>
       <c r="Q58" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>425.4593101840328</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>426.56214666880885</v>
       </c>
       <c r="R58">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3916460408342832E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4162820931422635E-2</v>
       </c>
     </row>
     <row r="59" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C59" s="2"/>
       <c r="G59" s="20">
-        <v>46136</v>
+        <v>46147</v>
       </c>
       <c r="H59">
-        <v>326.4273</v>
+        <v>327.22732000000002</v>
       </c>
       <c r="I59" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J59" s="26"/>
@@ -9189,36 +9142,36 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3900</v>
       </c>
       <c r="O59" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50119</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50124</v>
       </c>
       <c r="P59" cm="1">
         <f t="array" aca="1" ref="P59" ca="1">_xll.qwDataInterp(N59,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>430.47887881453318</v>
+        <v>431.79831424390284</v>
       </c>
       <c r="Q59" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>430.90935769334766</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>432.05739323244916</v>
       </c>
       <c r="R59">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3939562631152711E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4176635650823286E-2</v>
       </c>
     </row>
     <row r="60" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C60" s="2"/>
-      <c r="G60" s="20">
-        <v>46135</v>
-      </c>
-      <c r="H60" s="26">
-        <v>326.37619999999998</v>
+      <c r="G60" s="21">
+        <v>46146</v>
+      </c>
+      <c r="H60" s="22">
+        <v>327.11673999999999</v>
       </c>
       <c r="I60" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J60" s="26"/>
@@ -9226,36 +9179,36 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
       <c r="N60" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4000</v>
       </c>
       <c r="O60" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50219</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50224</v>
       </c>
       <c r="P60" cm="1">
         <f t="array" aca="1" ref="P60" ca="1">_xll.qwDataInterp(N60,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>433.36046096169667</v>
+        <v>434.67541514561481</v>
       </c>
       <c r="Q60" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>434.6605423445817</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>435.58823351742058</v>
       </c>
       <c r="R60">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3957323411686771E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4185610549574132E-2</v>
       </c>
     </row>
     <row r="61" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C61" s="2"/>
-      <c r="G61" s="20">
-        <v>46134</v>
-      </c>
-      <c r="H61">
-        <v>326.32510000000002</v>
+      <c r="G61" s="21">
+        <v>46143</v>
+      </c>
+      <c r="H61" s="22">
+        <v>326.78500000000003</v>
       </c>
       <c r="I61" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J61" s="26"/>
@@ -9263,36 +9216,36 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4100</v>
       </c>
       <c r="O61" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50319</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50324</v>
       </c>
       <c r="P61" cm="1">
         <f t="array" aca="1" ref="P61" ca="1">_xll.qwDataInterp(N61,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>436.24204310886017</v>
+        <v>437.55251604732683</v>
       </c>
       <c r="Q61" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>436.24204310886017</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>437.46500554411739</v>
       </c>
       <c r="R61">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3970187493786765E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4190153059766795E-2</v>
       </c>
     </row>
     <row r="62" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C62" s="2"/>
       <c r="G62" s="20">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="H62">
-        <v>326.274</v>
+        <v>326.73390000000001</v>
       </c>
       <c r="I62" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J62" s="26"/>
@@ -9300,36 +9253,36 @@
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4200</v>
       </c>
       <c r="O62" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50419</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50424</v>
       </c>
       <c r="P62" cm="1">
         <f t="array" aca="1" ref="P62" ca="1">_xll.qwDataInterp(N62,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>439.12362525602373</v>
+        <v>440.4296169490388</v>
       </c>
       <c r="Q62" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>437.36713075499961</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>438.75598440463244</v>
       </c>
       <c r="R62">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3978556291029074E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4190630841580685E-2</v>
       </c>
     </row>
     <row r="63" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C63" s="2"/>
       <c r="G63" s="20">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="H63">
-        <v>326.22289999999998</v>
+        <v>326.68279999999999</v>
       </c>
       <c r="I63" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J63" s="26"/>
@@ -9337,36 +9290,36 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4300</v>
       </c>
       <c r="O63" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50519</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50524</v>
       </c>
       <c r="P63" cm="1">
         <f t="array" aca="1" ref="P63" ca="1">_xll.qwDataInterp(N63,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>442.00520740318723</v>
+        <v>443.30671785075077</v>
       </c>
       <c r="Q63" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>443.33122302539675</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>444.32632330180746</v>
       </c>
       <c r="R63">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3982792941884989E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4187376425743645E-2</v>
       </c>
     </row>
     <row r="64" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C64" s="2"/>
       <c r="G64" s="20">
-        <v>46129</v>
+        <v>46140</v>
       </c>
       <c r="H64">
-        <v>326.06959999999998</v>
+        <v>326.63170000000002</v>
       </c>
       <c r="I64" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J64" s="26"/>
@@ -9374,36 +9327,36 @@
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4400</v>
       </c>
       <c r="O64" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50619</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50624</v>
       </c>
       <c r="P64" cm="1">
         <f t="array" aca="1" ref="P64" ca="1">_xll.qwDataInterp(N64,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>444.88678955035073</v>
+        <v>446.1838187524628</v>
       </c>
       <c r="Q64" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>445.7765631294514</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>446.98694962621727</v>
       </c>
       <c r="R64">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3983226676094649E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4180691223278261E-2</v>
       </c>
     </row>
     <row r="65" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C65" s="2"/>
       <c r="G65" s="20">
-        <v>46128</v>
-      </c>
-      <c r="H65" s="26">
-        <v>326.01850000000002</v>
+        <v>46139</v>
+      </c>
+      <c r="H65">
+        <v>326.5806</v>
       </c>
       <c r="I65" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J65" s="26"/>
@@ -9411,36 +9364,36 @@
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
       <c r="N65" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4500</v>
       </c>
       <c r="O65" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50719</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50724</v>
       </c>
       <c r="P65" cm="1">
         <f t="array" aca="1" ref="P65" ca="1">_xll.qwDataInterp(N65,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>447.76837169751423</v>
+        <v>449.06091965417477</v>
       </c>
       <c r="Q65" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>446.42506658242166</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>447.75864298717767</v>
       </c>
       <c r="R65">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3980156599211044E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.417084900080857E-2</v>
       </c>
     </row>
     <row r="66" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C66" s="2"/>
       <c r="G66" s="20">
-        <v>46127</v>
+        <v>46136</v>
       </c>
       <c r="H66">
-        <v>325.9674</v>
+        <v>326.4273</v>
       </c>
       <c r="I66" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J66" s="26"/>
@@ -9448,36 +9401,36 @@
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
       <c r="N66" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4600</v>
       </c>
       <c r="O66" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50819</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50824</v>
       </c>
       <c r="P66" cm="1">
         <f t="array" aca="1" ref="P66" ca="1">_xll.qwDataInterp(N66,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>450.64995384467773</v>
+        <v>451.93802055588674</v>
       </c>
       <c r="Q66" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>449.74865393698838</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>451.12453211888612</v>
       </c>
       <c r="R66">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3973854983711851E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4158098902635095E-2</v>
       </c>
     </row>
     <row r="67" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C67" s="2"/>
       <c r="G67" s="20">
-        <v>46126</v>
-      </c>
-      <c r="H67">
-        <v>325.91629999999998</v>
+        <v>46135</v>
+      </c>
+      <c r="H67" s="26">
+        <v>326.37619999999998</v>
       </c>
       <c r="I67" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J67" s="26"/>
@@ -9485,36 +9438,36 @@
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
       <c r="N67" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4700</v>
       </c>
       <c r="O67" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>50919</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>50924</v>
       </c>
       <c r="P67" cm="1">
         <f t="array" aca="1" ref="P67" ca="1">_xll.qwDataInterp(N67,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>453.53153599184128</v>
+        <v>454.81512145759876</v>
       </c>
       <c r="Q67" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>454.89213059981677</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>456.13408530982576</v>
       </c>
       <c r="R67">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3964570140053487E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4142668086988728E-2</v>
       </c>
     </row>
     <row r="68" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C68" s="2"/>
       <c r="G68" s="20">
-        <v>46125</v>
+        <v>46134</v>
       </c>
       <c r="H68">
-        <v>325.66079999999999</v>
+        <v>326.32510000000002</v>
       </c>
       <c r="I68" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J68" s="26"/>
@@ -9522,36 +9475,36 @@
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
       <c r="N68" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4800</v>
       </c>
       <c r="O68" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51019</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51024</v>
       </c>
       <c r="P68" cm="1">
         <f t="array" aca="1" ref="P68" ca="1">_xll.qwDataInterp(N68,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>456.41311813900478</v>
+        <v>457.69222235931073</v>
       </c>
       <c r="Q68" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>457.3259443752828</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>458.37876069284971</v>
       </c>
       <c r="R68">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3952528928840255E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4124764032660284E-2</v>
       </c>
     </row>
     <row r="69" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C69" s="2"/>
       <c r="G69" s="20">
-        <v>46121</v>
+        <v>46133</v>
       </c>
       <c r="H69">
-        <v>325.66079999999999</v>
+        <v>326.274</v>
       </c>
       <c r="I69" s="26">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J69" s="26"/>
@@ -9559,36 +9512,36 @@
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4900</v>
       </c>
       <c r="O69" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51119</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51124</v>
       </c>
       <c r="P69" cm="1">
         <f t="array" aca="1" ref="P69" ca="1">_xll.qwDataInterp(N69,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>459.29470028616828</v>
+        <v>460.5693232610227</v>
       </c>
       <c r="Q69" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>456.99822678473743</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>458.03619198308712</v>
       </c>
       <c r="R69">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3937938965303829E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4104576563035218E-2</v>
       </c>
     </row>
     <row r="70" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C70" s="2"/>
       <c r="G70" s="20">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="H70">
-        <v>325.60969999999998</v>
+        <v>326.22289999999998</v>
       </c>
       <c r="I70" s="26">
-        <f t="shared" ref="I70:I75" ca="1" si="23">IF((G70=$C$20),$D$20,0)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J70" s="26"/>
@@ -9596,37 +9549,37 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5000</v>
       </c>
       <c r="O70" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51219</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51224</v>
       </c>
       <c r="P70" cm="1">
         <f t="array" aca="1" ref="P70" ca="1">_xll.qwDataInterp(N70,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>462.17628243333178</v>
+        <v>463.44642416273473</v>
       </c>
       <c r="Q70" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>462.63845871576507</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>463.72449201723236</v>
       </c>
       <c r="R70">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3920990559116895E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4082279627057668E-2</v>
       </c>
     </row>
     <row r="71" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C71" s="2"/>
       <c r="F71" s="26"/>
       <c r="G71" s="20">
-        <v>46119</v>
+        <v>46129</v>
       </c>
       <c r="H71">
-        <v>325.55860000000001</v>
+        <v>326.06959999999998</v>
       </c>
       <c r="I71" s="26">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J71" s="26"/>
@@ -9634,37 +9587,37 @@
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5100</v>
       </c>
       <c r="O71" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51319</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51324</v>
       </c>
       <c r="P71" cm="1">
         <f t="array" aca="1" ref="P71" ca="1">_xll.qwDataInterp(N71,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>465.05786458049533</v>
+        <v>466.3235250644467</v>
       </c>
       <c r="Q71" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>465.98798030965634</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>467.30280446708201</v>
       </c>
       <c r="R71">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3901858425827482E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4058032870450718E-2</v>
       </c>
     </row>
     <row r="72" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C72" s="2"/>
       <c r="F72" s="26"/>
       <c r="G72" s="20">
-        <v>46118</v>
-      </c>
-      <c r="H72">
-        <v>325.50749999999999</v>
+        <v>46128</v>
+      </c>
+      <c r="H72" s="26">
+        <v>326.01850000000002</v>
       </c>
       <c r="I72" s="26">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="J72" s="26"/>
@@ -9672,37 +9625,37 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5200</v>
       </c>
       <c r="O72" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51419</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51424</v>
       </c>
       <c r="P72" cm="1">
         <f t="array" aca="1" ref="P72" ca="1">_xll.qwDataInterp(N72,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>467.93944672765883</v>
+        <v>469.20062596615867</v>
       </c>
       <c r="Q72" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>467.93944672765883</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>469.10678584096547</v>
       </c>
       <c r="R72">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3880703200619413E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4031983025404102E-2</v>
       </c>
     </row>
     <row r="73" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C73" s="2"/>
       <c r="F73" s="26"/>
-      <c r="G73" s="21">
-        <v>46114</v>
-      </c>
-      <c r="H73" s="22">
-        <v>325.30309999999997</v>
+      <c r="G73" s="20">
+        <v>46127</v>
+      </c>
+      <c r="H73">
+        <v>325.9674</v>
       </c>
       <c r="I73" s="26">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ref="I73:I81" ca="1" si="24">IF((G73=$C$20),$D$20,0)</f>
         <v>0</v>
       </c>
       <c r="J73" s="26"/>
@@ -9710,37 +9663,37 @@
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5300</v>
       </c>
       <c r="O73" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51519</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51524</v>
       </c>
       <c r="P73" cm="1">
         <f t="array" aca="1" ref="P73" ca="1">_xll.qwDataInterp(N73,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>470.82102887482233</v>
+        <v>472.07772686787064</v>
       </c>
       <c r="Q73" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>468.93774475932304</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>470.2838315057727</v>
       </c>
       <c r="R73">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3857672780486006E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.4004265142686165E-2</v>
       </c>
     </row>
     <row r="74" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C74" s="2"/>
       <c r="F74" s="26"/>
-      <c r="G74" s="21">
-        <v>46113</v>
-      </c>
-      <c r="H74" s="28">
-        <v>325.25200000000001</v>
+      <c r="G74" s="20">
+        <v>46126</v>
+      </c>
+      <c r="H74">
+        <v>325.91629999999998</v>
       </c>
       <c r="I74" s="26">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ca="1" si="24"/>
         <v>0</v>
       </c>
       <c r="J74" s="26"/>
@@ -9748,37 +9701,37 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5400</v>
       </c>
       <c r="O74" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51619</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51624</v>
       </c>
       <c r="P74" cm="1">
         <f t="array" aca="1" ref="P74" ca="1">_xll.qwDataInterp(N74,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>473.70261102198583</v>
+        <v>474.95482776958266</v>
       </c>
       <c r="Q74" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>475.12371885505172</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>476.37969225289135</v>
       </c>
       <c r="R74">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3832903517039705E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.3975003686593777E-2</v>
       </c>
     </row>
     <row r="75" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C75" s="2"/>
       <c r="F75" s="26"/>
       <c r="G75" s="20">
-        <v>46112</v>
-      </c>
-      <c r="H75" s="26">
-        <v>325.21334999999999</v>
+        <v>46125</v>
+      </c>
+      <c r="H75">
+        <v>325.66079999999999</v>
       </c>
       <c r="I75" s="26">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ca="1" si="24"/>
         <v>0</v>
       </c>
       <c r="J75" s="26"/>
@@ -9786,241 +9739,287 @@
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
       <c r="N75" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5500</v>
       </c>
       <c r="O75" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51719</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51724</v>
       </c>
       <c r="P75" cm="1">
         <f t="array" aca="1" ref="P75" ca="1">_xll.qwDataInterp(N75,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>476.62635451378543</v>
+        <v>477.87881123747593</v>
       </c>
       <c r="Q75" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>477.57960722281302</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>478.73899309770337</v>
       </c>
       <c r="R75">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3812531700752482E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.3950980393164123E-2</v>
       </c>
     </row>
     <row r="76" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C76" s="2"/>
       <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
+      <c r="G76" s="20">
+        <v>46121</v>
+      </c>
+      <c r="H76">
+        <v>325.66079999999999</v>
+      </c>
+      <c r="I76" s="26">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
+      </c>
       <c r="J76" s="26"/>
       <c r="K76" s="3"/>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
       <c r="N76" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5600</v>
       </c>
       <c r="O76" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51819</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51824</v>
       </c>
       <c r="P76" cm="1">
         <f t="array" aca="1" ref="P76" ca="1">_xll.qwDataInterp(N76,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>479.75594457057286</v>
+        <v>481.00266248751058</v>
       </c>
       <c r="Q76" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>478.31667673686115</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>479.60775476629681</v>
       </c>
       <c r="R76">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.381901454900226E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.3953054336175228E-2</v>
       </c>
     </row>
     <row r="77" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C77" s="2"/>
       <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="26"/>
-      <c r="I77" s="26"/>
+      <c r="G77" s="20">
+        <v>46120</v>
+      </c>
+      <c r="H77">
+        <v>325.60969999999998</v>
+      </c>
+      <c r="I77" s="26">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
+      </c>
       <c r="J77" s="26"/>
       <c r="K77" s="3"/>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
       <c r="N77" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5700</v>
       </c>
       <c r="O77" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>51919</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>51924</v>
       </c>
       <c r="P77" cm="1">
         <f t="array" aca="1" ref="P77" ca="1">_xll.qwDataInterp(N77,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>482.8855346273603</v>
+        <v>484.12651373754522</v>
       </c>
       <c r="Q77" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>481.91976355810556</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>483.25508601281763</v>
       </c>
       <c r="R77">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3822480080382347E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.3952289888784728E-2</v>
       </c>
     </row>
     <row r="78" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C78" s="2"/>
       <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26"/>
-      <c r="I78" s="26"/>
+      <c r="G78" s="20">
+        <v>46119</v>
+      </c>
+      <c r="H78">
+        <v>325.55860000000001</v>
+      </c>
+      <c r="I78" s="26">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
+      </c>
       <c r="J78" s="26"/>
       <c r="K78" s="3"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
       <c r="N78" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5800</v>
       </c>
       <c r="O78" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>52019</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>52024</v>
       </c>
       <c r="P78" cm="1">
         <f t="array" aca="1" ref="P78" ca="1">_xll.qwDataInterp(N78,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>486.01512468414774</v>
+        <v>487.25036498757987</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>487.47317005820014</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>488.66339104604378</v>
       </c>
       <c r="R78">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3823119759022848E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.3948868832866621E-2</v>
       </c>
     </row>
     <row r="79" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C79" s="2"/>
       <c r="F79" s="26"/>
-      <c r="G79" s="26"/>
-      <c r="H79" s="26"/>
-      <c r="I79" s="26"/>
+      <c r="G79" s="20">
+        <v>46118</v>
+      </c>
+      <c r="H79">
+        <v>325.50749999999999</v>
+      </c>
+      <c r="I79" s="26">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
+      </c>
       <c r="J79" s="26"/>
       <c r="K79" s="3"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5900</v>
       </c>
       <c r="O79" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>52119</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>52124</v>
       </c>
       <c r="P79" cm="1">
         <f t="array" aca="1" ref="P79" ca="1">_xll.qwDataInterp(N79,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>489.14471474093523</v>
+        <v>490.37421623761452</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>490.12300417041712</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>491.10977756197099</v>
       </c>
       <c r="R79">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3821111420772256E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.394295998687257E-2</v>
       </c>
     </row>
     <row r="80" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C80" s="2"/>
       <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
+      <c r="G80" s="21">
+        <v>46114</v>
+      </c>
+      <c r="H80" s="22">
+        <v>325.30309999999997</v>
+      </c>
+      <c r="I80" s="26">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
+      </c>
       <c r="J80" s="26"/>
       <c r="K80" s="3"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6000</v>
       </c>
       <c r="O80" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>52219</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>52224</v>
       </c>
       <c r="P80" cm="1">
         <f t="array" aca="1" ref="P80" ca="1">_xll.qwDataInterp(N80,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>492.27430479772266</v>
+        <v>493.49806748764917</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>489.81293327373407</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>490.78382811646713</v>
       </c>
       <c r="R80">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3816620422978607E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.3934720300134105E-2</v>
       </c>
     </row>
     <row r="81" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C81" s="2"/>
       <c r="F81" s="26"/>
-      <c r="G81" s="26"/>
-      <c r="H81" s="26"/>
-      <c r="I81" s="26"/>
+      <c r="G81" s="21">
+        <v>46113</v>
+      </c>
+      <c r="H81" s="28">
+        <v>325.25200000000001</v>
+      </c>
+      <c r="I81" s="26">
+        <f t="shared" ca="1" si="24"/>
+        <v>0</v>
+      </c>
       <c r="J81" s="26"/>
       <c r="K81" s="3"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6100</v>
       </c>
       <c r="O81" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>52319</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>52324</v>
       </c>
       <c r="P81" cm="1">
         <f t="array" aca="1" ref="P81" ca="1">_xll.qwDataInterp(N81,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>495.4038948545101</v>
+        <v>496.62191873768376</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>495.89929874936456</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>497.76414915078044</v>
       </c>
       <c r="R81">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3809800680947735E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.392429583928779E-2</v>
       </c>
     </row>
     <row r="82" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C82" s="2"/>
       <c r="F82" s="26"/>
-      <c r="G82" s="26"/>
-      <c r="H82" s="26"/>
+      <c r="G82" s="20">
+        <v>46112</v>
+      </c>
+      <c r="H82" s="26">
+        <v>325.21334999999999</v>
+      </c>
       <c r="I82" s="26"/>
       <c r="J82" s="26"/>
       <c r="K82" s="3"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6200</v>
       </c>
       <c r="O82" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>52419</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>52424</v>
       </c>
       <c r="P82" cm="1">
         <f t="array" aca="1" ref="P82" ca="1">_xll.qwDataInterp(N82,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>498.53348491129753</v>
+        <v>499.7457699877184</v>
       </c>
       <c r="Q82" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>499.53055188112012</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>500.79523610469261</v>
       </c>
       <c r="R82">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3800795603865055E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.3911822678989614E-2</v>
       </c>
     </row>
     <row r="83" spans="3:18" x14ac:dyDescent="0.25">
@@ -10034,24 +10033,24 @@
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
       <c r="N83" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6300</v>
       </c>
       <c r="O83" s="2">
-        <f t="shared" ca="1" si="20"/>
-        <v>52519</v>
+        <f t="shared" ca="1" si="21"/>
+        <v>52524</v>
       </c>
       <c r="P83" cm="1">
         <f t="array" aca="1" ref="P83" ca="1">_xll.qwDataInterp(N83,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>501.66307496808497</v>
+        <v>502.86962123775305</v>
       </c>
       <c r="Q83" s="3">
-        <f t="shared" ca="1" si="21"/>
-        <v>501.66307496808497</v>
+        <f t="shared" ca="1" si="22"/>
+        <v>502.7690473135055</v>
       </c>
       <c r="R83">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3789738941333294E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.3897427707541663E-2</v>
       </c>
     </row>
     <row r="84" spans="3:18" x14ac:dyDescent="0.25">
@@ -10065,24 +10064,24 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
       <c r="N84" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6400</v>
       </c>
       <c r="O84" s="2">
-        <f t="shared" ref="O84:O93" ca="1" si="24">N84+$D$10</f>
-        <v>52619</v>
+        <f t="shared" ref="O84:O93" ca="1" si="25">N84+$D$10</f>
+        <v>52624</v>
       </c>
       <c r="P84" cm="1">
         <f t="array" aca="1" ref="P84" ca="1">_xll.qwDataInterp(N84,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>504.79266502487241</v>
+        <v>505.9934724877877</v>
       </c>
       <c r="Q84" s="3">
-        <f t="shared" ref="Q84:Q93" ca="1" si="25">VLOOKUP(MONTH(O84),$AI$4:$AK$15,3,0)*P84</f>
-        <v>502.77349436477289</v>
+        <f t="shared" ref="Q84:Q93" ca="1" si="26">VLOOKUP(MONTH(O84),$AI$4:$AK$15,3,0)*P84</f>
+        <v>504.0706972923341</v>
       </c>
       <c r="R84">
-        <f t="shared" ca="1" si="22"/>
-        <v>2.3776755550301232E-2</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>2.3881229356736755E-2</v>
       </c>
     </row>
     <row r="85" spans="3:18" x14ac:dyDescent="0.25">
@@ -10096,24 +10095,24 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6500</v>
       </c>
       <c r="O85" s="2">
-        <f t="shared" ca="1" si="24"/>
-        <v>52719</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>52724</v>
       </c>
       <c r="P85" cm="1">
         <f t="array" aca="1" ref="P85" ca="1">_xll.qwDataInterp(N85,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>507.92225508165984</v>
+        <v>509.11732373782235</v>
       </c>
       <c r="Q85" s="3">
-        <f t="shared" ca="1" si="25"/>
-        <v>509.44602184690478</v>
+        <f t="shared" ca="1" si="26"/>
+        <v>510.64467570903577</v>
       </c>
       <c r="R85">
-        <f t="shared" ref="R85:R93" ca="1" si="26">EXP(LN(P85/$P$20)*1/((O85-$O$20)/365))-1</f>
-        <v>2.3761962090945055E-2</v>
+        <f t="shared" ref="R85:R93" ca="1" si="27">EXP(LN(P85/$P$20)*1/((O85-$O$20)/365))-1</f>
+        <v>2.3863338264072498E-2</v>
       </c>
     </row>
     <row r="86" spans="3:18" x14ac:dyDescent="0.25">
@@ -10127,24 +10126,24 @@
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
       <c r="N86" s="3">
-        <f t="shared" ref="N86:N93" si="27">N85+100</f>
+        <f t="shared" ref="N86:N93" si="28">N85+100</f>
         <v>6600</v>
       </c>
       <c r="O86" s="2">
-        <f t="shared" ca="1" si="24"/>
-        <v>52819</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>52824</v>
       </c>
       <c r="P86" cm="1">
         <f t="array" aca="1" ref="P86" ca="1">_xll.qwDataInterp(N86,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>511.05184513844733</v>
+        <v>512.24117498785699</v>
       </c>
       <c r="Q86" s="3">
-        <f t="shared" ca="1" si="25"/>
-        <v>512.07394882872427</v>
+        <f t="shared" ca="1" si="26"/>
+        <v>513.16320910283514</v>
       </c>
       <c r="R86">
-        <f t="shared" ca="1" si="26"/>
-        <v>2.3745467659038733E-2</v>
+        <f t="shared" ca="1" si="27"/>
+        <v>2.3843857874509711E-2</v>
       </c>
     </row>
     <row r="87" spans="3:18" x14ac:dyDescent="0.25">
@@ -10158,24 +10157,24 @@
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
       <c r="N87" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6700</v>
       </c>
       <c r="O87" s="2">
-        <f t="shared" ca="1" si="24"/>
-        <v>52919</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>52924</v>
       </c>
       <c r="P87" cm="1">
         <f t="array" aca="1" ref="P87" ca="1">_xll.qwDataInterp(N87,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>514.18143519523471</v>
+        <v>515.36502623789158</v>
       </c>
       <c r="Q87" s="3">
-        <f t="shared" ca="1" si="25"/>
-        <v>512.63889088964902</v>
+        <f t="shared" ca="1" si="26"/>
+        <v>513.87046766180174</v>
       </c>
       <c r="R87">
-        <f t="shared" ca="1" si="26"/>
-        <v>2.3727374361443454E-2</v>
+        <f t="shared" ca="1" si="27"/>
+        <v>2.3822884988087267E-2</v>
       </c>
     </row>
     <row r="88" spans="3:18" x14ac:dyDescent="0.25">
@@ -10189,24 +10188,24 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
       <c r="N88" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6800</v>
       </c>
       <c r="O88" s="2">
-        <f t="shared" ca="1" si="24"/>
-        <v>53019</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>53024</v>
       </c>
       <c r="P88" cm="1">
         <f t="array" aca="1" ref="P88" ca="1">_xll.qwDataInterp(N88,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>517.3110252520222</v>
+        <v>518.48887748792629</v>
       </c>
       <c r="Q88" s="3">
-        <f t="shared" ca="1" si="25"/>
-        <v>516.27640320151818</v>
+        <f t="shared" ca="1" si="26"/>
+        <v>518.799970814419</v>
       </c>
       <c r="R88">
-        <f t="shared" ca="1" si="26"/>
-        <v>2.370777784057343E-2</v>
+        <f t="shared" ca="1" si="27"/>
+        <v>2.3800510258970897E-2</v>
       </c>
     </row>
     <row r="89" spans="3:18" x14ac:dyDescent="0.25">
@@ -10220,24 +10219,24 @@
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
       <c r="N89" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6900</v>
       </c>
       <c r="O89" s="2">
-        <f t="shared" ca="1" si="24"/>
-        <v>53119</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>53124</v>
       </c>
       <c r="P89" cm="1">
         <f t="array" aca="1" ref="P89" ca="1">_xll.qwDataInterp(N89,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>520.44061530880958</v>
+        <v>521.61272873796088</v>
       </c>
       <c r="Q89" s="3">
-        <f t="shared" ca="1" si="25"/>
-        <v>522.00193715473597</v>
+        <f t="shared" ca="1" si="26"/>
+        <v>523.12540565130087</v>
       </c>
       <c r="R89">
-        <f t="shared" ca="1" si="26"/>
-        <v>2.3686767753013704E-2</v>
+        <f t="shared" ca="1" si="27"/>
+        <v>2.377681865086223E-2</v>
       </c>
     </row>
     <row r="90" spans="3:18" x14ac:dyDescent="0.25">
@@ -10251,24 +10250,24 @@
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
       <c r="N90" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7000</v>
       </c>
       <c r="O90" s="2">
-        <f t="shared" ca="1" si="24"/>
-        <v>53219</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>53224</v>
       </c>
       <c r="P90" cm="1">
         <f t="array" aca="1" ref="P90" ca="1">_xll.qwDataInterp(N90,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>523.57020536559708</v>
+        <v>524.73657998799558</v>
       </c>
       <c r="Q90" s="3">
-        <f t="shared" ca="1" si="25"/>
-        <v>524.61734577632831</v>
+        <f t="shared" ca="1" si="26"/>
+        <v>525.52368485797763</v>
       </c>
       <c r="R90">
-        <f t="shared" ca="1" si="26"/>
-        <v>2.3664428206877197E-2</v>
+        <f t="shared" ca="1" si="27"/>
+        <v>2.3751889853132813E-2</v>
       </c>
     </row>
     <row r="91" spans="3:18" x14ac:dyDescent="0.25">
@@ -10282,24 +10281,24 @@
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
       <c r="N91" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7100</v>
       </c>
       <c r="O91" s="2">
-        <f t="shared" ca="1" si="24"/>
-        <v>53319</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>53324</v>
       </c>
       <c r="P91" cm="1">
         <f t="array" aca="1" ref="P91" ca="1">_xll.qwDataInterp(N91,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>526.69979542238457</v>
+        <v>527.86043123803017</v>
       </c>
       <c r="Q91" s="3">
-        <f t="shared" ca="1" si="25"/>
-        <v>524.06629644527266</v>
+        <f t="shared" ca="1" si="26"/>
+        <v>524.95719886622101</v>
       </c>
       <c r="R91">
-        <f t="shared" ca="1" si="26"/>
-        <v>2.3640838161969047E-2</v>
+        <f t="shared" ca="1" si="27"/>
+        <v>2.3725798661563102E-2</v>
       </c>
     </row>
     <row r="92" spans="3:18" x14ac:dyDescent="0.25">
@@ -10313,24 +10312,24 @@
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
       <c r="N92" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7200</v>
       </c>
       <c r="O92" s="2">
-        <f t="shared" ca="1" si="24"/>
-        <v>53419</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>53424</v>
       </c>
       <c r="P92" cm="1">
         <f t="array" aca="1" ref="P92" ca="1">_xll.qwDataInterp(N92,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>529.82938547917195</v>
+        <v>530.98428248806476</v>
       </c>
       <c r="Q92" s="3">
-        <f t="shared" ca="1" si="25"/>
-        <v>531.41887363560943</v>
+        <f t="shared" ca="1" si="26"/>
+        <v>532.20554633778727</v>
       </c>
       <c r="R92">
-        <f t="shared" ca="1" si="26"/>
-        <v>2.3616071796380034E-2</v>
+        <f t="shared" ca="1" si="27"/>
+        <v>2.3698615327123695E-2</v>
       </c>
     </row>
     <row r="93" spans="3:18" x14ac:dyDescent="0.25">
@@ -10345,24 +10344,24 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7300</v>
       </c>
       <c r="O93" s="2">
-        <f t="shared" ca="1" si="24"/>
-        <v>53519</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>53524</v>
       </c>
       <c r="P93" cm="1">
         <f t="array" aca="1" ref="P93" ca="1">_xll.qwDataInterp(N93,$A$20:$A$44,$D$20:$D$44,4)</f>
-        <v>532.95897553595944</v>
+        <v>534.10813373809947</v>
       </c>
       <c r="Q93" s="3">
-        <f t="shared" ca="1" si="25"/>
-        <v>534.02489348703136</v>
+        <f t="shared" ca="1" si="26"/>
+        <v>535.22976081894944</v>
       </c>
       <c r="R93">
-        <f t="shared" ca="1" si="26"/>
-        <v>2.3590198842727839E-2</v>
+        <f t="shared" ca="1" si="27"/>
+        <v>2.3670405875873879E-2</v>
       </c>
     </row>
     <row r="94" spans="3:18" x14ac:dyDescent="0.25">
@@ -11569,7 +11568,7 @@
       </c>
       <c r="I2">
         <f>_xll.BDP(G2, "PX_LAST")</f>
-        <v>333.97989999999999</v>
+        <v>334.13659999999999</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -11591,7 +11590,7 @@
       </c>
       <c r="I3">
         <f>_xll.BDP(G3, "PX_LAST")</f>
-        <v>335.64</v>
+        <v>336.1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -11613,7 +11612,7 @@
       </c>
       <c r="I4">
         <f>_xll.BDP(G4, "PX_LAST")</f>
-        <v>335.06990000000002</v>
+        <v>335.46980000000002</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -11635,7 +11634,7 @@
       </c>
       <c r="I5">
         <f>_xll.BDP(G5, "PX_LAST")</f>
-        <v>340.1841</v>
+        <v>340.64</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -11657,7 +11656,7 @@
       </c>
       <c r="I6">
         <f>_xll.BDP(G6, "PX_LAST")</f>
-        <v>336.42</v>
+        <v>336.85</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -11679,7 +11678,7 @@
       </c>
       <c r="I7">
         <f>_xll.BDP(G7, "PX_LAST")</f>
-        <v>341.81659999999999</v>
+        <v>342.40989999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -11701,7 +11700,7 @@
       </c>
       <c r="I8">
         <f>_xll.BDP(G8, "PX_LAST")</f>
-        <v>339.05860000000001</v>
+        <v>339.59</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -11723,7 +11722,7 @@
       </c>
       <c r="I9">
         <f>_xll.BDP(G9, "PX_LAST")</f>
-        <v>341.22640000000001</v>
+        <v>341.64</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -11745,7 +11744,7 @@
       </c>
       <c r="I10">
         <f>_xll.BDP(G10, "PX_LAST")</f>
-        <v>335.51</v>
+        <v>335.96980000000002</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -11767,7 +11766,7 @@
       </c>
       <c r="I11">
         <f>_xll.BDP(G11, "PX_LAST")</f>
-        <v>337.69</v>
+        <v>338.11989999999997</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -11789,7 +11788,7 @@
       </c>
       <c r="I12">
         <f>_xll.BDP(G12, "PX_LAST")</f>
-        <v>335.11</v>
+        <v>335.50990000000002</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -11811,7 +11810,7 @@
       </c>
       <c r="I13">
         <f>_xll.BDP(G13, "PX_LAST")</f>
-        <v>335.09</v>
+        <v>335.50990000000002</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -13121,7 +13120,7 @@
       </c>
       <c r="C73">
         <f>_xll.BDP(A73, "PX_LAST")</f>
-        <v>1.9449000000000001</v>
+        <v>2.0363000000000002</v>
       </c>
       <c r="G73" t="s">
         <v>311</v>
@@ -13143,7 +13142,7 @@
       </c>
       <c r="C74">
         <f>_xll.BDP(A74, "PX_LAST")</f>
-        <v>2.2675000000000001</v>
+        <v>2.3210000000000002</v>
       </c>
       <c r="G74" t="s">
         <v>314</v>
@@ -13165,7 +13164,7 @@
       </c>
       <c r="C75">
         <f>_xll.BDP(A75, "PX_LAST")</f>
-        <v>2.3567</v>
+        <v>2.3948999999999998</v>
       </c>
       <c r="G75" t="s">
         <v>317</v>
@@ -13187,7 +13186,7 @@
       </c>
       <c r="C76">
         <f>_xll.BDP(A76, "PX_LAST")</f>
-        <v>2.3889999999999998</v>
+        <v>2.42</v>
       </c>
       <c r="G76" t="s">
         <v>320</v>
@@ -13209,7 +13208,7 @@
       </c>
       <c r="C77">
         <f>_xll.BDP(A77, "PX_LAST")</f>
-        <v>2.4020000000000001</v>
+        <v>2.4329000000000001</v>
       </c>
       <c r="G77" t="s">
         <v>323</v>
@@ -13231,7 +13230,7 @@
       </c>
       <c r="C78">
         <f>_xll.BDP(A78, "PX_LAST")</f>
-        <v>2.403</v>
+        <v>2.4327000000000001</v>
       </c>
       <c r="G78" t="s">
         <v>326</v>
@@ -13253,7 +13252,7 @@
       </c>
       <c r="C79">
         <f>_xll.BDP(A79, "PX_LAST")</f>
-        <v>2.3978999999999999</v>
+        <v>2.4257</v>
       </c>
       <c r="G79" t="s">
         <v>329</v>
@@ -13275,7 +13274,7 @@
       </c>
       <c r="C80">
         <f>_xll.BDP(A80, "PX_LAST")</f>
-        <v>2.3925000000000001</v>
+        <v>2.4199000000000002</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -13287,7 +13286,7 @@
       </c>
       <c r="C81">
         <f>_xll.BDP(A81, "PX_LAST")</f>
-        <v>2.3898000000000001</v>
+        <v>2.4156</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -13299,7 +13298,7 @@
       </c>
       <c r="C82">
         <f>_xll.BDP(A82, "PX_LAST")</f>
-        <v>2.3925000000000001</v>
+        <v>2.4169999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -13311,7 +13310,7 @@
       </c>
       <c r="C83">
         <f>_xll.BDP(A83, "PX_LAST")</f>
-        <v>2.3938000000000001</v>
+        <v>2.4127000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -13323,7 +13322,7 @@
       </c>
       <c r="C84">
         <f>_xll.BDP(A84, "PX_LAST")</f>
-        <v>2.3849999999999998</v>
+        <v>2.3978999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -13335,7 +13334,7 @@
       </c>
       <c r="C85">
         <f>_xll.BDP(A85, "PX_LAST")</f>
-        <v>2.3620000000000001</v>
+        <v>2.3693</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -13347,7 +13346,7 @@
       </c>
       <c r="C86">
         <f>_xll.BDP(A86, "PX_LAST")</f>
-        <v>2.3330000000000002</v>
+        <v>2.3348</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -13359,7 +13358,7 @@
       </c>
       <c r="C87">
         <f>_xll.BDP(A87, "PX_LAST")</f>
-        <v>2.3340000000000001</v>
+        <v>2.3365</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
